--- a/Planejamento Geral.xlsx
+++ b/Planejamento Geral.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr filterPrivacy="1" updateLinks="always" codeName="EstaPastaDeTrabalho"/>
-  <xr:revisionPtr revIDLastSave="5827" documentId="13_ncr:1_{8CB3FCBC-DACE-4BCA-A656-CE7D6185D885}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BB6EA715-C200-4F18-A922-A051548662E0}"/>
+  <xr:revisionPtr revIDLastSave="5828" documentId="13_ncr:1_{8CB3FCBC-DACE-4BCA-A656-CE7D6185D885}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1009D19F-397B-44B6-ADDC-DAE847083D56}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="363" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -15,7 +15,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Embarques Vivenciais'!$A$76:$H$97</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Equipe!$A$1:$H$54</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Equipe!$A$1:$H$53</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Planejamento IED'!$A$1:$E$1011</definedName>
     <definedName name="Hoje" localSheetId="3">TODAY()</definedName>
     <definedName name="Hoje" localSheetId="0">TODAY()</definedName>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2027" uniqueCount="491">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2020" uniqueCount="491">
   <si>
     <t>Nome</t>
   </si>
@@ -3310,363 +3310,6 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFB381D9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFB381D9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFB381D9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFB381D9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFB381D9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFB381D9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFB381D9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFB381D9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFB381D9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFB381D9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFB381D9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFB381D9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFB381D9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFB381D9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFB381D9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFB381D9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFB381D9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
           <bgColor theme="7"/>
         </patternFill>
       </fill>
@@ -3796,6 +3439,363 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFB381D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFB381D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFB381D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFB381D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFB381D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFB381D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFB381D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFB381D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFB381D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFB381D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFB381D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFB381D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFB381D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFB381D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFB381D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFB381D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFB381D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFB381D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -20416,9 +20416,9 @@
       <c r="A349" s="85" t="s">
         <v>248</v>
       </c>
-      <c r="B349" s="98">
+      <c r="B349" s="98" t="str">
         <f>_xlfn.XLOOKUP(A349,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v>9678697</v>
+        <v/>
       </c>
       <c r="C349" s="88">
         <v>45676</v>
@@ -20438,11 +20438,11 @@
       </c>
       <c r="H349" s="85" t="str">
         <f>_xlfn.XLOOKUP(Tabela1[[#This Row],[Matrícula]],Equipe!B:B,Equipe!E:E,"ERRO",0)</f>
-        <v>PBAC</v>
-      </c>
-      <c r="I349" s="85" t="str">
-        <f>VLOOKUP(Tabela1[[#This Row],[Matrícula]],Equipe!B:F,5,0)</f>
-        <v>Experiente</v>
+        <v>ERRO</v>
+      </c>
+      <c r="I349" s="85" t="e">
+        <f>VLOOKUP(Tabela1[[#This Row],[Matrícula]],Equipe!B:F,5,0)</f>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="350" spans="1:9" x14ac:dyDescent="0.25">
@@ -22747,9 +22747,9 @@
       <c r="A421" s="85" t="s">
         <v>248</v>
       </c>
-      <c r="B421" s="98">
+      <c r="B421" s="98" t="str">
         <f>_xlfn.XLOOKUP(A421,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v>9678697</v>
+        <v/>
       </c>
       <c r="C421" s="88">
         <v>46072</v>
@@ -22769,20 +22769,20 @@
       </c>
       <c r="H421" s="85" t="str">
         <f>_xlfn.XLOOKUP(Tabela1[[#This Row],[Matrícula]],Equipe!B:B,Equipe!E:E,"ERRO",0)</f>
-        <v>PBAC</v>
-      </c>
-      <c r="I421" s="85" t="str">
-        <f>VLOOKUP(Tabela1[[#This Row],[Matrícula]],Equipe!B:F,5,0)</f>
-        <v>Experiente</v>
+        <v>ERRO</v>
+      </c>
+      <c r="I421" s="85" t="e">
+        <f>VLOOKUP(Tabela1[[#This Row],[Matrícula]],Equipe!B:F,5,0)</f>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="422" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A422" s="85" t="s">
         <v>248</v>
       </c>
-      <c r="B422" s="98">
+      <c r="B422" s="98" t="str">
         <f>_xlfn.XLOOKUP(A422,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v>9678697</v>
+        <v/>
       </c>
       <c r="C422" s="88">
         <v>46086</v>
@@ -22802,11 +22802,11 @@
       </c>
       <c r="H422" s="85" t="str">
         <f>_xlfn.XLOOKUP(Tabela1[[#This Row],[Matrícula]],Equipe!B:B,Equipe!E:E,"ERRO",0)</f>
-        <v>PBAC</v>
-      </c>
-      <c r="I422" s="85" t="str">
-        <f>VLOOKUP(Tabela1[[#This Row],[Matrícula]],Equipe!B:F,5,0)</f>
-        <v>Experiente</v>
+        <v>ERRO</v>
+      </c>
+      <c r="I422" s="85" t="e">
+        <f>VLOOKUP(Tabela1[[#This Row],[Matrícula]],Equipe!B:F,5,0)</f>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="423" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -24784,9 +24784,9 @@
       <c r="A483" s="85" t="s">
         <v>248</v>
       </c>
-      <c r="B483" s="98">
+      <c r="B483" s="98" t="str">
         <f>_xlfn.XLOOKUP(A483,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v>9678697</v>
+        <v/>
       </c>
       <c r="C483" s="88">
         <v>46329</v>
@@ -24806,11 +24806,11 @@
       </c>
       <c r="H483" s="85" t="str">
         <f>_xlfn.XLOOKUP(Tabela1[[#This Row],[Matrícula]],Equipe!B:B,Equipe!E:E,"ERRO",0)</f>
-        <v>PBAC</v>
-      </c>
-      <c r="I483" s="85" t="str">
-        <f>VLOOKUP(Tabela1[[#This Row],[Matrícula]],Equipe!B:F,5,0)</f>
-        <v>Experiente</v>
+        <v>ERRO</v>
+      </c>
+      <c r="I483" s="85" t="e">
+        <f>VLOOKUP(Tabela1[[#This Row],[Matrícula]],Equipe!B:F,5,0)</f>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="484" spans="1:9" x14ac:dyDescent="0.25">
@@ -25223,9 +25223,9 @@
     </row>
     <row r="500" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A500" s="85"/>
-      <c r="B500" s="98" t="str">
+      <c r="B500" s="98">
         <f>_xlfn.XLOOKUP(A500,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C500" s="88"/>
       <c r="D500" s="99" t="str">
@@ -25246,9 +25246,9 @@
     </row>
     <row r="501" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A501" s="85"/>
-      <c r="B501" s="98">
+      <c r="B501" s="98" t="str">
         <f>_xlfn.XLOOKUP(A501,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C501" s="88"/>
       <c r="D501" s="99" t="str">
@@ -25292,9 +25292,9 @@
     </row>
     <row r="503" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A503" s="85"/>
-      <c r="B503" s="98">
+      <c r="B503" s="98" t="str">
         <f>_xlfn.XLOOKUP(A503,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C503" s="88"/>
       <c r="D503" s="99" t="str">
@@ -25430,9 +25430,9 @@
     </row>
     <row r="509" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A509" s="85"/>
-      <c r="B509" s="98">
+      <c r="B509" s="98" t="str">
         <f>_xlfn.XLOOKUP(A509,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C509" s="88"/>
       <c r="D509" s="99" t="str">
@@ -25453,9 +25453,9 @@
     </row>
     <row r="510" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A510" s="85"/>
-      <c r="B510" s="98">
+      <c r="B510" s="98" t="str">
         <f>_xlfn.XLOOKUP(A510,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C510" s="88"/>
       <c r="D510" s="99" t="str">
@@ -25522,9 +25522,9 @@
     </row>
     <row r="513" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A513" s="85"/>
-      <c r="B513" s="98" t="str">
+      <c r="B513" s="98">
         <f>_xlfn.XLOOKUP(A513,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C513" s="88"/>
       <c r="D513" s="99" t="str">
@@ -25568,9 +25568,9 @@
     </row>
     <row r="515" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A515" s="85"/>
-      <c r="B515" s="98">
+      <c r="B515" s="98" t="str">
         <f>_xlfn.XLOOKUP(A515,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C515" s="88"/>
       <c r="D515" s="99" t="str">
@@ -25683,9 +25683,9 @@
     </row>
     <row r="520" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A520" s="85"/>
-      <c r="B520" s="98">
+      <c r="B520" s="98" t="str">
         <f>_xlfn.XLOOKUP(A520,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C520" s="88"/>
       <c r="D520" s="99" t="str">
@@ -25752,9 +25752,9 @@
     </row>
     <row r="523" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A523" s="85"/>
-      <c r="B523" s="98">
+      <c r="B523" s="98" t="str">
         <f>_xlfn.XLOOKUP(A523,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C523" s="88"/>
       <c r="D523" s="99" t="str">
@@ -25775,9 +25775,9 @@
     </row>
     <row r="524" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A524" s="85"/>
-      <c r="B524" s="98">
+      <c r="B524" s="98" t="str">
         <f>_xlfn.XLOOKUP(A524,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C524" s="88"/>
       <c r="D524" s="99" t="str">
@@ -25798,9 +25798,9 @@
     </row>
     <row r="525" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A525" s="85"/>
-      <c r="B525" s="98">
+      <c r="B525" s="98" t="str">
         <f>_xlfn.XLOOKUP(A525,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C525" s="88"/>
       <c r="D525" s="99" t="str">
@@ -25890,9 +25890,9 @@
     </row>
     <row r="529" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A529" s="85"/>
-      <c r="B529" s="98">
+      <c r="B529" s="98" t="str">
         <f>_xlfn.XLOOKUP(A529,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C529" s="88"/>
       <c r="D529" s="99" t="str">
@@ -25936,9 +25936,9 @@
     </row>
     <row r="531" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A531" s="85"/>
-      <c r="B531" s="98">
+      <c r="B531" s="98" t="str">
         <f>_xlfn.XLOOKUP(A531,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C531" s="88"/>
       <c r="D531" s="99" t="str">
@@ -26028,9 +26028,9 @@
     </row>
     <row r="535" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A535" s="85"/>
-      <c r="B535" s="98">
+      <c r="B535" s="98" t="str">
         <f>_xlfn.XLOOKUP(A535,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C535" s="88"/>
       <c r="D535" s="99" t="str">
@@ -26097,9 +26097,9 @@
     </row>
     <row r="538" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A538" s="85"/>
-      <c r="B538" s="98">
+      <c r="B538" s="98" t="str">
         <f>_xlfn.XLOOKUP(A538,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C538" s="88"/>
       <c r="D538" s="99" t="str">
@@ -26212,9 +26212,9 @@
     </row>
     <row r="543" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A543" s="85"/>
-      <c r="B543" s="98">
+      <c r="B543" s="98" t="str">
         <f>_xlfn.XLOOKUP(A543,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C543" s="88"/>
       <c r="D543" s="99" t="str">
@@ -26235,9 +26235,9 @@
     </row>
     <row r="544" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A544" s="85"/>
-      <c r="B544" s="98" t="str">
+      <c r="B544" s="98">
         <f>_xlfn.XLOOKUP(A544,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C544" s="88"/>
       <c r="D544" s="99" t="str">
@@ -26327,9 +26327,9 @@
     </row>
     <row r="548" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A548" s="85"/>
-      <c r="B548" s="98">
+      <c r="B548" s="98" t="str">
         <f>_xlfn.XLOOKUP(A548,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C548" s="88"/>
       <c r="D548" s="99" t="str">
@@ -26534,9 +26534,9 @@
     </row>
     <row r="557" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A557" s="85"/>
-      <c r="B557" s="98">
+      <c r="B557" s="98" t="str">
         <f>_xlfn.XLOOKUP(A557,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C557" s="88"/>
       <c r="D557" s="99" t="str">
@@ -26672,9 +26672,9 @@
     </row>
     <row r="563" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A563" s="85"/>
-      <c r="B563" s="98">
+      <c r="B563" s="98" t="str">
         <f>_xlfn.XLOOKUP(A563,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C563" s="88"/>
       <c r="D563" s="99" t="str">
@@ -26718,9 +26718,9 @@
     </row>
     <row r="565" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A565" s="85"/>
-      <c r="B565" s="98">
+      <c r="B565" s="98" t="str">
         <f>_xlfn.XLOOKUP(A565,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C565" s="88"/>
       <c r="D565" s="99" t="str">
@@ -26764,9 +26764,9 @@
     </row>
     <row r="567" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A567" s="85"/>
-      <c r="B567" s="98">
+      <c r="B567" s="98" t="str">
         <f>_xlfn.XLOOKUP(A567,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C567" s="88"/>
       <c r="D567" s="99" t="str">
@@ -26810,9 +26810,9 @@
     </row>
     <row r="569" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A569" s="85"/>
-      <c r="B569" s="98" t="str">
+      <c r="B569" s="98">
         <f>_xlfn.XLOOKUP(A569,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C569" s="88"/>
       <c r="D569" s="99" t="str">
@@ -26833,9 +26833,9 @@
     </row>
     <row r="570" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A570" s="85"/>
-      <c r="B570" s="98" t="str">
+      <c r="B570" s="98">
         <f>_xlfn.XLOOKUP(A570,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C570" s="88"/>
       <c r="D570" s="99" t="str">
@@ -26856,9 +26856,9 @@
     </row>
     <row r="571" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A571" s="85"/>
-      <c r="B571" s="98">
+      <c r="B571" s="98" t="str">
         <f>_xlfn.XLOOKUP(A571,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C571" s="88"/>
       <c r="D571" s="99" t="str">
@@ -26879,9 +26879,9 @@
     </row>
     <row r="572" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A572" s="85"/>
-      <c r="B572" s="98">
+      <c r="B572" s="98" t="str">
         <f>_xlfn.XLOOKUP(A572,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C572" s="88"/>
       <c r="D572" s="99" t="str">
@@ -26902,9 +26902,9 @@
     </row>
     <row r="573" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A573" s="85"/>
-      <c r="B573" s="98">
+      <c r="B573" s="98" t="str">
         <f>_xlfn.XLOOKUP(A573,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C573" s="88"/>
       <c r="D573" s="99" t="str">
@@ -26971,9 +26971,9 @@
     </row>
     <row r="576" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A576" s="85"/>
-      <c r="B576" s="98">
+      <c r="B576" s="98" t="str">
         <f>_xlfn.XLOOKUP(A576,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C576" s="88"/>
       <c r="D576" s="99" t="str">
@@ -27178,9 +27178,9 @@
     </row>
     <row r="585" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A585" s="85"/>
-      <c r="B585" s="98">
+      <c r="B585" s="98" t="str">
         <f>_xlfn.XLOOKUP(A585,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C585" s="88"/>
       <c r="D585" s="99" t="str">
@@ -27316,9 +27316,9 @@
     </row>
     <row r="591" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A591" s="85"/>
-      <c r="B591" s="98">
+      <c r="B591" s="98" t="str">
         <f>_xlfn.XLOOKUP(A591,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C591" s="88"/>
       <c r="D591" s="99" t="str">
@@ -27431,9 +27431,9 @@
     </row>
     <row r="596" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A596" s="85"/>
-      <c r="B596" s="98">
+      <c r="B596" s="98" t="str">
         <f>_xlfn.XLOOKUP(A596,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C596" s="88"/>
       <c r="D596" s="99" t="str">
@@ -27500,9 +27500,9 @@
     </row>
     <row r="599" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A599" s="85"/>
-      <c r="B599" s="98">
+      <c r="B599" s="98" t="str">
         <f>_xlfn.XLOOKUP(A599,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C599" s="88"/>
       <c r="D599" s="99" t="str">
@@ -27523,9 +27523,9 @@
     </row>
     <row r="600" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A600" s="85"/>
-      <c r="B600" s="98" t="str">
+      <c r="B600" s="98">
         <f>_xlfn.XLOOKUP(A600,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C600" s="88"/>
       <c r="D600" s="99" t="str">
@@ -27615,9 +27615,9 @@
     </row>
     <row r="604" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A604" s="85"/>
-      <c r="B604" s="98">
+      <c r="B604" s="98" t="str">
         <f>_xlfn.XLOOKUP(A604,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C604" s="88"/>
       <c r="D604" s="99" t="str">
@@ -27638,9 +27638,9 @@
     </row>
     <row r="605" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A605" s="85"/>
-      <c r="B605" s="98">
+      <c r="B605" s="98" t="str">
         <f>_xlfn.XLOOKUP(A605,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C605" s="88"/>
       <c r="D605" s="99" t="str">
@@ -27822,9 +27822,9 @@
     </row>
     <row r="613" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A613" s="85"/>
-      <c r="B613" s="98">
+      <c r="B613" s="98" t="str">
         <f>_xlfn.XLOOKUP(A613,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C613" s="88"/>
       <c r="D613" s="99" t="str">
@@ -27868,9 +27868,9 @@
     </row>
     <row r="615" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A615" s="85"/>
-      <c r="B615" s="98">
+      <c r="B615" s="98" t="str">
         <f>_xlfn.XLOOKUP(A615,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C615" s="88"/>
       <c r="D615" s="99" t="str">
@@ -28006,9 +28006,9 @@
     </row>
     <row r="621" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A621" s="85"/>
-      <c r="B621" s="98">
+      <c r="B621" s="98" t="str">
         <f>_xlfn.XLOOKUP(A621,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C621" s="88"/>
       <c r="D621" s="99" t="str">
@@ -28121,9 +28121,9 @@
     </row>
     <row r="626" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A626" s="85"/>
-      <c r="B626" s="98" t="str">
+      <c r="B626" s="98">
         <f>_xlfn.XLOOKUP(A626,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C626" s="88"/>
       <c r="D626" s="99" t="str">
@@ -28167,9 +28167,9 @@
     </row>
     <row r="628" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A628" s="85"/>
-      <c r="B628" s="98">
+      <c r="B628" s="98" t="str">
         <f>_xlfn.XLOOKUP(A628,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C628" s="88"/>
       <c r="D628" s="99" t="str">
@@ -28190,9 +28190,9 @@
     </row>
     <row r="629" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A629" s="85"/>
-      <c r="B629" s="98">
+      <c r="B629" s="98" t="str">
         <f>_xlfn.XLOOKUP(A629,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C629" s="88"/>
       <c r="D629" s="99" t="str">
@@ -28259,9 +28259,9 @@
     </row>
     <row r="632" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A632" s="85"/>
-      <c r="B632" s="98">
+      <c r="B632" s="98" t="str">
         <f>_xlfn.XLOOKUP(A632,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C632" s="88"/>
       <c r="D632" s="99" t="str">
@@ -28351,9 +28351,9 @@
     </row>
     <row r="636" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A636" s="85"/>
-      <c r="B636" s="98">
+      <c r="B636" s="98" t="str">
         <f>_xlfn.XLOOKUP(A636,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C636" s="88"/>
       <c r="D636" s="99" t="str">
@@ -28374,9 +28374,9 @@
     </row>
     <row r="637" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A637" s="85"/>
-      <c r="B637" s="98">
+      <c r="B637" s="98" t="str">
         <f>_xlfn.XLOOKUP(A637,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C637" s="88"/>
       <c r="D637" s="99" t="str">
@@ -28397,9 +28397,9 @@
     </row>
     <row r="638" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A638" s="85"/>
-      <c r="B638" s="98">
+      <c r="B638" s="98" t="str">
         <f>_xlfn.XLOOKUP(A638,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C638" s="88"/>
       <c r="D638" s="99" t="str">
@@ -28420,9 +28420,9 @@
     </row>
     <row r="639" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A639" s="85"/>
-      <c r="B639" s="98" t="str">
+      <c r="B639" s="98">
         <f>_xlfn.XLOOKUP(A639,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C639" s="88"/>
       <c r="D639" s="99" t="str">
@@ -28466,9 +28466,9 @@
     </row>
     <row r="641" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A641" s="85"/>
-      <c r="B641" s="98">
+      <c r="B641" s="98" t="str">
         <f>_xlfn.XLOOKUP(A641,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C641" s="88"/>
       <c r="D641" s="99" t="str">
@@ -28604,9 +28604,9 @@
     </row>
     <row r="647" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A647" s="85"/>
-      <c r="B647" s="98">
+      <c r="B647" s="98" t="str">
         <f>_xlfn.XLOOKUP(A647,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C647" s="88"/>
       <c r="D647" s="99" t="str">
@@ -28650,9 +28650,9 @@
     </row>
     <row r="649" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A649" s="85"/>
-      <c r="B649" s="98">
+      <c r="B649" s="98" t="str">
         <f>_xlfn.XLOOKUP(A649,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C649" s="88"/>
       <c r="D649" s="99" t="str">
@@ -28719,9 +28719,9 @@
     </row>
     <row r="652" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A652" s="85"/>
-      <c r="B652" s="98">
+      <c r="B652" s="98" t="str">
         <f>_xlfn.XLOOKUP(A652,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C652" s="88"/>
       <c r="D652" s="99" t="str">
@@ -28788,9 +28788,9 @@
     </row>
     <row r="655" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A655" s="85"/>
-      <c r="B655" s="98">
+      <c r="B655" s="98" t="str">
         <f>_xlfn.XLOOKUP(A655,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C655" s="88"/>
       <c r="D655" s="99" t="str">
@@ -28903,9 +28903,9 @@
     </row>
     <row r="660" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A660" s="85"/>
-      <c r="B660" s="98">
+      <c r="B660" s="98" t="str">
         <f>_xlfn.XLOOKUP(A660,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C660" s="88"/>
       <c r="D660" s="99" t="str">
@@ -29041,9 +29041,9 @@
     </row>
     <row r="666" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A666" s="85"/>
-      <c r="B666" s="98" t="str">
+      <c r="B666" s="98">
         <f>_xlfn.XLOOKUP(A666,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C666" s="88"/>
       <c r="D666" s="99" t="str">
@@ -29087,9 +29087,9 @@
     </row>
     <row r="668" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A668" s="85"/>
-      <c r="B668" s="98" t="str">
+      <c r="B668" s="98">
         <f>_xlfn.XLOOKUP(A668,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C668" s="88"/>
       <c r="D668" s="99" t="str">
@@ -29110,9 +29110,9 @@
     </row>
     <row r="669" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A669" s="85"/>
-      <c r="B669" s="98">
+      <c r="B669" s="98" t="str">
         <f>_xlfn.XLOOKUP(A669,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C669" s="88"/>
       <c r="D669" s="99" t="str">
@@ -29133,9 +29133,9 @@
     </row>
     <row r="670" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A670" s="85"/>
-      <c r="B670" s="98" t="str">
+      <c r="B670" s="98">
         <f>_xlfn.XLOOKUP(A670,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C670" s="88"/>
       <c r="D670" s="99" t="str">
@@ -29156,9 +29156,9 @@
     </row>
     <row r="671" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A671" s="85"/>
-      <c r="B671" s="98">
+      <c r="B671" s="98" t="str">
         <f>_xlfn.XLOOKUP(A671,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C671" s="88"/>
       <c r="D671" s="99" t="str">
@@ -29225,9 +29225,9 @@
     </row>
     <row r="674" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A674" s="85"/>
-      <c r="B674" s="98">
+      <c r="B674" s="98" t="str">
         <f>_xlfn.XLOOKUP(A674,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C674" s="88"/>
       <c r="D674" s="99" t="str">
@@ -29248,9 +29248,9 @@
     </row>
     <row r="675" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A675" s="85"/>
-      <c r="B675" s="98">
+      <c r="B675" s="98" t="str">
         <f>_xlfn.XLOOKUP(A675,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C675" s="88"/>
       <c r="D675" s="99" t="str">
@@ -29340,9 +29340,9 @@
     </row>
     <row r="679" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A679" s="85"/>
-      <c r="B679" s="98">
+      <c r="B679" s="98" t="str">
         <f>_xlfn.XLOOKUP(A679,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C679" s="88"/>
       <c r="D679" s="99" t="str">
@@ -29363,9 +29363,9 @@
     </row>
     <row r="680" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A680" s="85"/>
-      <c r="B680" s="98">
+      <c r="B680" s="98" t="str">
         <f>_xlfn.XLOOKUP(A680,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C680" s="88"/>
       <c r="D680" s="99" t="str">
@@ -29455,9 +29455,9 @@
     </row>
     <row r="684" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A684" s="85"/>
-      <c r="B684" s="98">
+      <c r="B684" s="98" t="str">
         <f>_xlfn.XLOOKUP(A684,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C684" s="88"/>
       <c r="D684" s="99" t="str">
@@ -29570,9 +29570,9 @@
     </row>
     <row r="689" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A689" s="85"/>
-      <c r="B689" s="98">
+      <c r="B689" s="98" t="str">
         <f>_xlfn.XLOOKUP(A689,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C689" s="88"/>
       <c r="D689" s="99" t="str">
@@ -29616,9 +29616,9 @@
     </row>
     <row r="691" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A691" s="85"/>
-      <c r="B691" s="98">
+      <c r="B691" s="98" t="str">
         <f>_xlfn.XLOOKUP(A691,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C691" s="88"/>
       <c r="D691" s="99" t="str">
@@ -29708,9 +29708,9 @@
     </row>
     <row r="695" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A695" s="85"/>
-      <c r="B695" s="98" t="str">
+      <c r="B695" s="98">
         <f>_xlfn.XLOOKUP(A695,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C695" s="88"/>
       <c r="D695" s="99" t="str">
@@ -29754,9 +29754,9 @@
     </row>
     <row r="697" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A697" s="85"/>
-      <c r="B697" s="98">
+      <c r="B697" s="98" t="str">
         <f>_xlfn.XLOOKUP(A697,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C697" s="88"/>
       <c r="D697" s="99" t="str">
@@ -29915,9 +29915,9 @@
     </row>
     <row r="704" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A704" s="85"/>
-      <c r="B704" s="98">
+      <c r="B704" s="98" t="str">
         <f>_xlfn.XLOOKUP(A704,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C704" s="88"/>
       <c r="D704" s="99" t="str">
@@ -29961,9 +29961,9 @@
     </row>
     <row r="706" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A706" s="85"/>
-      <c r="B706" s="98">
+      <c r="B706" s="98" t="str">
         <f>_xlfn.XLOOKUP(A706,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C706" s="88"/>
       <c r="D706" s="99" t="str">
@@ -30076,9 +30076,9 @@
     </row>
     <row r="711" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A711" s="85"/>
-      <c r="B711" s="98">
+      <c r="B711" s="98" t="str">
         <f>_xlfn.XLOOKUP(A711,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C711" s="88"/>
       <c r="D711" s="99" t="str">
@@ -30122,9 +30122,9 @@
     </row>
     <row r="713" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A713" s="85"/>
-      <c r="B713" s="98">
+      <c r="B713" s="98" t="str">
         <f>_xlfn.XLOOKUP(A713,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C713" s="88"/>
       <c r="D713" s="99" t="str">
@@ -30191,9 +30191,9 @@
     </row>
     <row r="716" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A716" s="85"/>
-      <c r="B716" s="98">
+      <c r="B716" s="98" t="str">
         <f>_xlfn.XLOOKUP(A716,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C716" s="88"/>
       <c r="D716" s="99" t="str">
@@ -30329,9 +30329,9 @@
     </row>
     <row r="722" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A722" s="85"/>
-      <c r="B722" s="98">
+      <c r="B722" s="98" t="str">
         <f>_xlfn.XLOOKUP(A722,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C722" s="88"/>
       <c r="D722" s="99" t="str">
@@ -30398,9 +30398,9 @@
     </row>
     <row r="725" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A725" s="85"/>
-      <c r="B725" s="98">
+      <c r="B725" s="98" t="str">
         <f>_xlfn.XLOOKUP(A725,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C725" s="88"/>
       <c r="D725" s="99" t="str">
@@ -30513,9 +30513,9 @@
     </row>
     <row r="730" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A730" s="85"/>
-      <c r="B730" s="98">
+      <c r="B730" s="98" t="str">
         <f>_xlfn.XLOOKUP(A730,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C730" s="88"/>
       <c r="D730" s="99" t="str">
@@ -30582,9 +30582,9 @@
     </row>
     <row r="733" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A733" s="85"/>
-      <c r="B733" s="98">
+      <c r="B733" s="98" t="str">
         <f>_xlfn.XLOOKUP(A733,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C733" s="88"/>
       <c r="D733" s="99" t="str">
@@ -30605,9 +30605,9 @@
     </row>
     <row r="734" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A734" s="85"/>
-      <c r="B734" s="98">
+      <c r="B734" s="98" t="str">
         <f>_xlfn.XLOOKUP(A734,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C734" s="88"/>
       <c r="D734" s="99" t="str">
@@ -30628,9 +30628,9 @@
     </row>
     <row r="735" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A735" s="85"/>
-      <c r="B735" s="98">
+      <c r="B735" s="98" t="str">
         <f>_xlfn.XLOOKUP(A735,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C735" s="88"/>
       <c r="D735" s="99" t="str">
@@ -30651,9 +30651,9 @@
     </row>
     <row r="736" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A736" s="85"/>
-      <c r="B736" s="98">
+      <c r="B736" s="98" t="str">
         <f>_xlfn.XLOOKUP(A736,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C736" s="88"/>
       <c r="D736" s="99" t="str">
@@ -30720,9 +30720,9 @@
     </row>
     <row r="739" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A739" s="85"/>
-      <c r="B739" s="98">
+      <c r="B739" s="98" t="str">
         <f>_xlfn.XLOOKUP(A739,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C739" s="88"/>
       <c r="D739" s="99" t="str">
@@ -30858,9 +30858,9 @@
     </row>
     <row r="745" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A745" s="85"/>
-      <c r="B745" s="98">
+      <c r="B745" s="98" t="str">
         <f>_xlfn.XLOOKUP(A745,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C745" s="88"/>
       <c r="D745" s="99" t="str">
@@ -30950,9 +30950,9 @@
     </row>
     <row r="749" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A749" s="85"/>
-      <c r="B749" s="98">
+      <c r="B749" s="98" t="str">
         <f>_xlfn.XLOOKUP(A749,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C749" s="88"/>
       <c r="D749" s="99" t="str">
@@ -30973,9 +30973,9 @@
     </row>
     <row r="750" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A750" s="85"/>
-      <c r="B750" s="98" t="str">
+      <c r="B750" s="98">
         <f>_xlfn.XLOOKUP(A750,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C750" s="88"/>
       <c r="D750" s="99" t="str">
@@ -30996,9 +30996,9 @@
     </row>
     <row r="751" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A751" s="85"/>
-      <c r="B751" s="98" t="str">
+      <c r="B751" s="98">
         <f>_xlfn.XLOOKUP(A751,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C751" s="88"/>
       <c r="D751" s="99" t="str">
@@ -31019,9 +31019,9 @@
     </row>
     <row r="752" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A752" s="85"/>
-      <c r="B752" s="98" t="str">
+      <c r="B752" s="98">
         <f>_xlfn.XLOOKUP(A752,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C752" s="88"/>
       <c r="D752" s="99" t="str">
@@ -31042,9 +31042,9 @@
     </row>
     <row r="753" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A753" s="85"/>
-      <c r="B753" s="98">
+      <c r="B753" s="98" t="str">
         <f>_xlfn.XLOOKUP(A753,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C753" s="88"/>
       <c r="D753" s="99" t="str">
@@ -31157,9 +31157,9 @@
     </row>
     <row r="758" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A758" s="85"/>
-      <c r="B758" s="98">
+      <c r="B758" s="98" t="str">
         <f>_xlfn.XLOOKUP(A758,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C758" s="88"/>
       <c r="D758" s="99" t="str">
@@ -31180,9 +31180,9 @@
     </row>
     <row r="759" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A759" s="85"/>
-      <c r="B759" s="98">
+      <c r="B759" s="98" t="str">
         <f>_xlfn.XLOOKUP(A759,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C759" s="88"/>
       <c r="D759" s="99" t="str">
@@ -31203,9 +31203,9 @@
     </row>
     <row r="760" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A760" s="85"/>
-      <c r="B760" s="98">
+      <c r="B760" s="98" t="str">
         <f>_xlfn.XLOOKUP(A760,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C760" s="88"/>
       <c r="D760" s="99" t="str">
@@ -31226,9 +31226,9 @@
     </row>
     <row r="761" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A761" s="85"/>
-      <c r="B761" s="98">
+      <c r="B761" s="98" t="str">
         <f>_xlfn.XLOOKUP(A761,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C761" s="88"/>
       <c r="D761" s="99" t="str">
@@ -31295,9 +31295,9 @@
     </row>
     <row r="764" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A764" s="85"/>
-      <c r="B764" s="98">
+      <c r="B764" s="98" t="str">
         <f>_xlfn.XLOOKUP(A764,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C764" s="88"/>
       <c r="D764" s="99" t="str">
@@ -31410,9 +31410,9 @@
     </row>
     <row r="769" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A769" s="85"/>
-      <c r="B769" s="98">
+      <c r="B769" s="98" t="str">
         <f>_xlfn.XLOOKUP(A769,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C769" s="88"/>
       <c r="D769" s="99" t="str">
@@ -31456,9 +31456,9 @@
     </row>
     <row r="771" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A771" s="85"/>
-      <c r="B771" s="98">
+      <c r="B771" s="98" t="str">
         <f>_xlfn.XLOOKUP(A771,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C771" s="88"/>
       <c r="D771" s="99" t="str">
@@ -31571,9 +31571,9 @@
     </row>
     <row r="776" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A776" s="85"/>
-      <c r="B776" s="98">
+      <c r="B776" s="98" t="str">
         <f>_xlfn.XLOOKUP(A776,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C776" s="88"/>
       <c r="D776" s="99" t="str">
@@ -31686,9 +31686,9 @@
     </row>
     <row r="781" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A781" s="85"/>
-      <c r="B781" s="98">
+      <c r="B781" s="98" t="str">
         <f>_xlfn.XLOOKUP(A781,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C781" s="88"/>
       <c r="D781" s="99" t="str">
@@ -31801,9 +31801,9 @@
     </row>
     <row r="786" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A786" s="85"/>
-      <c r="B786" s="98">
+      <c r="B786" s="98" t="str">
         <f>_xlfn.XLOOKUP(A786,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C786" s="88"/>
       <c r="D786" s="99" t="str">
@@ -31847,9 +31847,9 @@
     </row>
     <row r="788" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A788" s="85"/>
-      <c r="B788" s="98">
+      <c r="B788" s="98" t="str">
         <f>_xlfn.XLOOKUP(A788,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C788" s="88"/>
       <c r="D788" s="99" t="str">
@@ -32008,9 +32008,9 @@
     </row>
     <row r="795" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A795" s="85"/>
-      <c r="B795" s="98">
+      <c r="B795" s="98" t="str">
         <f>_xlfn.XLOOKUP(A795,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C795" s="88"/>
       <c r="D795" s="99" t="str">
@@ -32031,9 +32031,9 @@
     </row>
     <row r="796" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A796" s="85"/>
-      <c r="B796" s="98">
+      <c r="B796" s="98" t="str">
         <f>_xlfn.XLOOKUP(A796,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C796" s="88"/>
       <c r="D796" s="99" t="str">
@@ -32054,9 +32054,9 @@
     </row>
     <row r="797" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A797" s="85"/>
-      <c r="B797" s="98">
+      <c r="B797" s="98" t="str">
         <f>_xlfn.XLOOKUP(A797,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C797" s="88"/>
       <c r="D797" s="99" t="str">
@@ -32123,9 +32123,9 @@
     </row>
     <row r="800" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A800" s="85"/>
-      <c r="B800" s="98">
+      <c r="B800" s="98" t="str">
         <f>_xlfn.XLOOKUP(A800,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C800" s="88"/>
       <c r="D800" s="99" t="str">
@@ -32261,9 +32261,9 @@
     </row>
     <row r="806" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A806" s="85"/>
-      <c r="B806" s="98">
+      <c r="B806" s="98" t="str">
         <f>_xlfn.XLOOKUP(A806,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C806" s="88"/>
       <c r="D806" s="99" t="str">
@@ -32330,9 +32330,9 @@
     </row>
     <row r="809" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A809" s="85"/>
-      <c r="B809" s="98">
+      <c r="B809" s="98" t="str">
         <f>_xlfn.XLOOKUP(A809,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C809" s="88"/>
       <c r="D809" s="99" t="str">
@@ -32468,9 +32468,9 @@
     </row>
     <row r="815" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A815" s="85"/>
-      <c r="B815" s="98">
+      <c r="B815" s="98" t="str">
         <f>_xlfn.XLOOKUP(A815,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C815" s="88"/>
       <c r="D815" s="99" t="str">
@@ -32514,9 +32514,9 @@
     </row>
     <row r="817" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A817" s="85"/>
-      <c r="B817" s="98">
+      <c r="B817" s="98" t="str">
         <f>_xlfn.XLOOKUP(A817,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C817" s="88"/>
       <c r="D817" s="99" t="str">
@@ -32560,9 +32560,9 @@
     </row>
     <row r="819" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A819" s="85"/>
-      <c r="B819" s="98">
+      <c r="B819" s="98" t="str">
         <f>_xlfn.XLOOKUP(A819,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C819" s="88"/>
       <c r="D819" s="99" t="str">
@@ -32629,9 +32629,9 @@
     </row>
     <row r="822" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A822" s="85"/>
-      <c r="B822" s="98" t="str">
+      <c r="B822" s="98">
         <f>_xlfn.XLOOKUP(A822,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C822" s="88"/>
       <c r="D822" s="99" t="str">
@@ -32652,9 +32652,9 @@
     </row>
     <row r="823" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A823" s="85"/>
-      <c r="B823" s="98">
+      <c r="B823" s="98" t="str">
         <f>_xlfn.XLOOKUP(A823,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C823" s="88"/>
       <c r="D823" s="99" t="str">
@@ -32675,9 +32675,9 @@
     </row>
     <row r="824" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A824" s="85"/>
-      <c r="B824" s="98" t="str">
+      <c r="B824" s="98">
         <f>_xlfn.XLOOKUP(A824,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C824" s="88"/>
       <c r="D824" s="99" t="str">
@@ -32698,9 +32698,9 @@
     </row>
     <row r="825" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A825" s="85"/>
-      <c r="B825" s="98">
+      <c r="B825" s="98" t="str">
         <f>_xlfn.XLOOKUP(A825,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C825" s="88"/>
       <c r="D825" s="99" t="str">
@@ -32744,9 +32744,9 @@
     </row>
     <row r="827" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A827" s="85"/>
-      <c r="B827" s="98" t="str">
+      <c r="B827" s="98">
         <f>_xlfn.XLOOKUP(A827,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C827" s="88"/>
       <c r="D827" s="99" t="str">
@@ -32882,9 +32882,9 @@
     </row>
     <row r="833" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A833" s="85"/>
-      <c r="B833" s="98">
+      <c r="B833" s="98" t="str">
         <f>_xlfn.XLOOKUP(A833,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C833" s="88"/>
       <c r="D833" s="99" t="str">
@@ -32997,9 +32997,9 @@
     </row>
     <row r="838" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A838" s="85"/>
-      <c r="B838" s="98">
+      <c r="B838" s="98" t="str">
         <f>_xlfn.XLOOKUP(A838,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C838" s="88"/>
       <c r="D838" s="99" t="str">
@@ -33066,9 +33066,9 @@
     </row>
     <row r="841" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A841" s="85"/>
-      <c r="B841" s="98">
+      <c r="B841" s="98" t="str">
         <f>_xlfn.XLOOKUP(A841,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C841" s="88"/>
       <c r="D841" s="99" t="str">
@@ -33089,9 +33089,9 @@
     </row>
     <row r="842" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A842" s="85"/>
-      <c r="B842" s="98">
+      <c r="B842" s="98" t="str">
         <f>_xlfn.XLOOKUP(A842,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C842" s="88"/>
       <c r="D842" s="99" t="str">
@@ -33181,9 +33181,9 @@
     </row>
     <row r="846" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A846" s="85"/>
-      <c r="B846" s="98">
+      <c r="B846" s="98" t="str">
         <f>_xlfn.XLOOKUP(A846,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C846" s="88"/>
       <c r="D846" s="99" t="str">
@@ -33250,9 +33250,9 @@
     </row>
     <row r="849" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A849" s="85"/>
-      <c r="B849" s="98" t="str">
+      <c r="B849" s="98">
         <f>_xlfn.XLOOKUP(A849,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C849" s="88"/>
       <c r="D849" s="99" t="str">
@@ -33296,9 +33296,9 @@
     </row>
     <row r="851" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A851" s="85"/>
-      <c r="B851" s="98">
+      <c r="B851" s="98" t="str">
         <f>_xlfn.XLOOKUP(A851,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C851" s="88"/>
       <c r="D851" s="99" t="str">
@@ -33549,9 +33549,9 @@
     </row>
     <row r="862" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A862" s="85"/>
-      <c r="B862" s="98">
+      <c r="B862" s="98" t="str">
         <f>_xlfn.XLOOKUP(A862,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C862" s="88"/>
       <c r="D862" s="99" t="str">
@@ -33618,9 +33618,9 @@
     </row>
     <row r="865" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A865" s="85"/>
-      <c r="B865" s="98">
+      <c r="B865" s="98" t="str">
         <f>_xlfn.XLOOKUP(A865,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C865" s="88"/>
       <c r="D865" s="99" t="str">
@@ -33641,9 +33641,9 @@
     </row>
     <row r="866" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A866" s="85"/>
-      <c r="B866" s="98" t="str">
+      <c r="B866" s="98">
         <f>_xlfn.XLOOKUP(A866,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C866" s="88"/>
       <c r="D866" s="99" t="str">
@@ -33664,9 +33664,9 @@
     </row>
     <row r="867" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A867" s="85"/>
-      <c r="B867" s="98">
+      <c r="B867" s="98" t="str">
         <f>_xlfn.XLOOKUP(A867,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C867" s="88"/>
       <c r="D867" s="99" t="str">
@@ -33779,9 +33779,9 @@
     </row>
     <row r="872" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A872" s="85"/>
-      <c r="B872" s="98">
+      <c r="B872" s="98" t="str">
         <f>_xlfn.XLOOKUP(A872,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C872" s="88"/>
       <c r="D872" s="99" t="str">
@@ -33802,9 +33802,9 @@
     </row>
     <row r="873" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A873" s="85"/>
-      <c r="B873" s="98">
+      <c r="B873" s="98" t="str">
         <f>_xlfn.XLOOKUP(A873,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C873" s="88"/>
       <c r="D873" s="99" t="str">
@@ -33848,9 +33848,9 @@
     </row>
     <row r="875" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A875" s="85"/>
-      <c r="B875" s="98">
+      <c r="B875" s="98" t="str">
         <f>_xlfn.XLOOKUP(A875,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C875" s="88"/>
       <c r="D875" s="99" t="str">
@@ -33940,9 +33940,9 @@
     </row>
     <row r="879" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A879" s="85"/>
-      <c r="B879" s="98">
+      <c r="B879" s="98" t="str">
         <f>_xlfn.XLOOKUP(A879,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C879" s="88"/>
       <c r="D879" s="99" t="str">
@@ -33963,9 +33963,9 @@
     </row>
     <row r="880" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A880" s="85"/>
-      <c r="B880" s="98">
+      <c r="B880" s="98" t="str">
         <f>_xlfn.XLOOKUP(A880,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C880" s="88"/>
       <c r="D880" s="99" t="str">
@@ -34032,9 +34032,9 @@
     </row>
     <row r="883" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A883" s="85"/>
-      <c r="B883" s="98">
+      <c r="B883" s="98" t="str">
         <f>_xlfn.XLOOKUP(A883,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C883" s="88"/>
       <c r="D883" s="99" t="str">
@@ -34078,9 +34078,9 @@
     </row>
     <row r="885" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A885" s="85"/>
-      <c r="B885" s="98">
+      <c r="B885" s="98" t="str">
         <f>_xlfn.XLOOKUP(A885,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C885" s="88"/>
       <c r="D885" s="99" t="str">
@@ -34147,9 +34147,9 @@
     </row>
     <row r="888" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A888" s="85"/>
-      <c r="B888" s="98">
+      <c r="B888" s="98" t="str">
         <f>_xlfn.XLOOKUP(A888,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C888" s="88"/>
       <c r="D888" s="99" t="str">
@@ -34262,9 +34262,9 @@
     </row>
     <row r="893" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A893" s="85"/>
-      <c r="B893" s="98">
+      <c r="B893" s="98" t="str">
         <f>_xlfn.XLOOKUP(A893,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C893" s="88"/>
       <c r="D893" s="99" t="str">
@@ -34308,9 +34308,9 @@
     </row>
     <row r="895" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A895" s="85"/>
-      <c r="B895" s="98">
+      <c r="B895" s="98" t="str">
         <f>_xlfn.XLOOKUP(A895,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C895" s="88"/>
       <c r="D895" s="99" t="str">
@@ -34377,9 +34377,9 @@
     </row>
     <row r="898" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A898" s="85"/>
-      <c r="B898" s="98" t="str">
+      <c r="B898" s="98">
         <f>_xlfn.XLOOKUP(A898,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C898" s="88"/>
       <c r="D898" s="99" t="str">
@@ -34515,9 +34515,9 @@
     </row>
     <row r="904" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A904" s="85"/>
-      <c r="B904" s="98">
+      <c r="B904" s="98" t="str">
         <f>_xlfn.XLOOKUP(A904,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C904" s="88"/>
       <c r="D904" s="99" t="str">
@@ -34538,9 +34538,9 @@
     </row>
     <row r="905" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A905" s="85"/>
-      <c r="B905" s="98" t="str">
+      <c r="B905" s="98">
         <f>_xlfn.XLOOKUP(A905,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C905" s="88"/>
       <c r="D905" s="99" t="str">
@@ -34584,9 +34584,9 @@
     </row>
     <row r="907" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A907" s="85"/>
-      <c r="B907" s="98">
+      <c r="B907" s="98" t="str">
         <f>_xlfn.XLOOKUP(A907,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C907" s="88"/>
       <c r="D907" s="99" t="str">
@@ -34745,9 +34745,9 @@
     </row>
     <row r="914" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A914" s="85"/>
-      <c r="B914" s="98">
+      <c r="B914" s="98" t="str">
         <f>_xlfn.XLOOKUP(A914,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C914" s="88"/>
       <c r="D914" s="99" t="str">
@@ -34768,9 +34768,9 @@
     </row>
     <row r="915" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A915" s="85"/>
-      <c r="B915" s="98">
+      <c r="B915" s="98" t="str">
         <f>_xlfn.XLOOKUP(A915,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C915" s="88"/>
       <c r="D915" s="99" t="str">
@@ -34791,9 +34791,9 @@
     </row>
     <row r="916" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A916" s="85"/>
-      <c r="B916" s="98">
+      <c r="B916" s="98" t="str">
         <f>_xlfn.XLOOKUP(A916,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C916" s="88"/>
       <c r="D916" s="99" t="str">
@@ -35021,9 +35021,9 @@
     </row>
     <row r="926" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A926" s="85"/>
-      <c r="B926" s="98">
+      <c r="B926" s="98" t="str">
         <f>_xlfn.XLOOKUP(A926,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C926" s="88"/>
       <c r="D926" s="99" t="str">
@@ -35136,9 +35136,9 @@
     </row>
     <row r="931" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A931" s="85"/>
-      <c r="B931" s="98">
+      <c r="B931" s="98" t="str">
         <f>_xlfn.XLOOKUP(A931,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C931" s="88"/>
       <c r="D931" s="99" t="str">
@@ -35228,9 +35228,9 @@
     </row>
     <row r="935" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A935" s="85"/>
-      <c r="B935" s="98">
+      <c r="B935" s="98" t="str">
         <f>_xlfn.XLOOKUP(A935,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C935" s="88"/>
       <c r="D935" s="99" t="str">
@@ -35320,9 +35320,9 @@
     </row>
     <row r="939" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A939" s="85"/>
-      <c r="B939" s="98">
+      <c r="B939" s="98" t="str">
         <f>_xlfn.XLOOKUP(A939,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C939" s="88"/>
       <c r="D939" s="99" t="str">
@@ -35527,9 +35527,9 @@
     </row>
     <row r="948" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A948" s="85"/>
-      <c r="B948" s="98" t="str">
+      <c r="B948" s="98">
         <f>_xlfn.XLOOKUP(A948,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C948" s="88"/>
       <c r="D948" s="99" t="str">
@@ -35550,9 +35550,9 @@
     </row>
     <row r="949" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A949" s="85"/>
-      <c r="B949" s="98">
+      <c r="B949" s="98" t="str">
         <f>_xlfn.XLOOKUP(A949,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C949" s="88"/>
       <c r="D949" s="99" t="str">
@@ -35573,9 +35573,9 @@
     </row>
     <row r="950" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A950" s="85"/>
-      <c r="B950" s="98">
+      <c r="B950" s="98" t="str">
         <f>_xlfn.XLOOKUP(A950,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C950" s="88"/>
       <c r="D950" s="99" t="str">
@@ -35596,9 +35596,9 @@
     </row>
     <row r="951" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A951" s="85"/>
-      <c r="B951" s="98">
+      <c r="B951" s="98" t="str">
         <f>_xlfn.XLOOKUP(A951,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C951" s="88"/>
       <c r="D951" s="99" t="str">
@@ -35642,9 +35642,9 @@
     </row>
     <row r="953" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A953" s="85"/>
-      <c r="B953" s="98" t="str">
+      <c r="B953" s="98">
         <f>_xlfn.XLOOKUP(A953,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C953" s="88"/>
       <c r="D953" s="99" t="str">
@@ -35665,9 +35665,9 @@
     </row>
     <row r="954" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A954" s="85"/>
-      <c r="B954" s="98" t="str">
+      <c r="B954" s="98">
         <f>_xlfn.XLOOKUP(A954,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C954" s="88"/>
       <c r="D954" s="99" t="str">
@@ -35780,9 +35780,9 @@
     </row>
     <row r="959" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A959" s="85"/>
-      <c r="B959" s="98">
+      <c r="B959" s="98" t="str">
         <f>_xlfn.XLOOKUP(A959,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C959" s="88"/>
       <c r="D959" s="99" t="str">
@@ -35803,9 +35803,9 @@
     </row>
     <row r="960" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A960" s="85"/>
-      <c r="B960" s="98">
+      <c r="B960" s="98" t="str">
         <f>_xlfn.XLOOKUP(A960,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C960" s="88"/>
       <c r="D960" s="99" t="str">
@@ -35872,9 +35872,9 @@
     </row>
     <row r="963" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A963" s="85"/>
-      <c r="B963" s="98">
+      <c r="B963" s="98" t="str">
         <f>_xlfn.XLOOKUP(A963,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C963" s="88"/>
       <c r="D963" s="99" t="str">
@@ -35895,9 +35895,9 @@
     </row>
     <row r="964" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A964" s="85"/>
-      <c r="B964" s="98" t="str">
+      <c r="B964" s="98">
         <f>_xlfn.XLOOKUP(A964,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C964" s="88"/>
       <c r="D964" s="99" t="str">
@@ -35964,9 +35964,9 @@
     </row>
     <row r="967" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A967" s="85"/>
-      <c r="B967" s="98">
+      <c r="B967" s="98" t="str">
         <f>_xlfn.XLOOKUP(A967,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C967" s="88"/>
       <c r="D967" s="99" t="str">
@@ -36010,9 +36010,9 @@
     </row>
     <row r="969" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A969" s="85"/>
-      <c r="B969" s="98">
+      <c r="B969" s="98" t="str">
         <f>_xlfn.XLOOKUP(A969,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C969" s="88"/>
       <c r="D969" s="99" t="str">
@@ -36056,9 +36056,9 @@
     </row>
     <row r="971" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A971" s="85"/>
-      <c r="B971" s="98">
+      <c r="B971" s="98" t="str">
         <f>_xlfn.XLOOKUP(A971,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C971" s="88"/>
       <c r="D971" s="99" t="str">
@@ -36079,9 +36079,9 @@
     </row>
     <row r="972" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A972" s="85"/>
-      <c r="B972" s="98">
+      <c r="B972" s="98" t="str">
         <f>_xlfn.XLOOKUP(A972,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C972" s="88"/>
       <c r="D972" s="99" t="str">
@@ -36148,9 +36148,9 @@
     </row>
     <row r="975" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A975" s="85"/>
-      <c r="B975" s="98" t="str">
+      <c r="B975" s="98">
         <f>_xlfn.XLOOKUP(A975,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C975" s="88"/>
       <c r="D975" s="99" t="str">
@@ -36194,9 +36194,9 @@
     </row>
     <row r="977" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A977" s="85"/>
-      <c r="B977" s="98">
+      <c r="B977" s="98" t="str">
         <f>_xlfn.XLOOKUP(A977,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C977" s="88"/>
       <c r="D977" s="99" t="str">
@@ -36240,9 +36240,9 @@
     </row>
     <row r="979" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A979" s="85"/>
-      <c r="B979" s="98">
+      <c r="B979" s="98" t="str">
         <f>_xlfn.XLOOKUP(A979,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C979" s="88"/>
       <c r="D979" s="99" t="str">
@@ -36286,9 +36286,9 @@
     </row>
     <row r="981" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A981" s="85"/>
-      <c r="B981" s="98">
+      <c r="B981" s="98" t="str">
         <f>_xlfn.XLOOKUP(A981,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C981" s="88"/>
       <c r="D981" s="99" t="str">
@@ -36355,9 +36355,9 @@
     </row>
     <row r="984" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A984" s="85"/>
-      <c r="B984" s="98">
+      <c r="B984" s="98" t="str">
         <f>_xlfn.XLOOKUP(A984,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C984" s="88"/>
       <c r="D984" s="99" t="str">
@@ -36424,9 +36424,9 @@
     </row>
     <row r="987" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A987" s="85"/>
-      <c r="B987" s="98">
+      <c r="B987" s="98" t="str">
         <f>_xlfn.XLOOKUP(A987,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C987" s="88"/>
       <c r="D987" s="99" t="str">
@@ -36516,9 +36516,9 @@
     </row>
     <row r="991" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A991" s="85"/>
-      <c r="B991" s="98">
+      <c r="B991" s="98" t="str">
         <f>_xlfn.XLOOKUP(A991,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C991" s="88"/>
       <c r="D991" s="99" t="str">
@@ -36608,9 +36608,9 @@
     </row>
     <row r="995" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A995" s="85"/>
-      <c r="B995" s="98">
+      <c r="B995" s="98" t="str">
         <f>_xlfn.XLOOKUP(A995,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C995" s="88"/>
       <c r="D995" s="99" t="str">
@@ -36631,9 +36631,9 @@
     </row>
     <row r="996" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A996" s="85"/>
-      <c r="B996" s="98">
+      <c r="B996" s="98" t="str">
         <f>_xlfn.XLOOKUP(A996,Equipe!H:H,Equipe!B:B,"",0)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C996" s="88"/>
       <c r="D996" s="99" t="str">
@@ -37040,9 +37040,9 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{317D2C0B-2A7B-4719-83E8-C2EBB7FA9A39}">
           <x14:formula1>
-            <xm:f>Equipe!$H$2:$H$125</xm:f>
+            <xm:f>Equipe!$H$2:$H$124</xm:f>
           </x14:formula1>
-          <xm:sqref>A362:A387 A2:A352 A390:A418 A421:A1008</xm:sqref>
+          <xm:sqref>A362:A387 A421:A1008 A390:A418 A2:A352</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -37053,7 +37053,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCFC853D-4B89-47CE-AA8F-BD4EA9CD1EC0}">
   <sheetPr codeName="Planilha1"/>
-  <dimension ref="A1:H56"/>
+  <dimension ref="A1:H55"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.5703125" style="5" bestFit="1" customWidth="1"/>
@@ -37770,210 +37770,210 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="79" t="s">
-        <v>331</v>
-      </c>
-      <c r="B28" s="107">
-        <v>9678697</v>
-      </c>
-      <c r="C28" s="107" t="s">
-        <v>432</v>
-      </c>
-      <c r="D28" s="107" t="s">
-        <v>320</v>
-      </c>
-      <c r="E28" s="81" t="s">
+        <v>318</v>
+      </c>
+      <c r="B28" s="101">
+        <v>4606246</v>
+      </c>
+      <c r="C28" s="101" t="s">
+        <v>386</v>
+      </c>
+      <c r="D28" s="101" t="s">
+        <v>387</v>
+      </c>
+      <c r="E28" s="80" t="s">
         <v>280</v>
       </c>
-      <c r="F28" s="109" t="s">
-        <v>333</v>
-      </c>
-      <c r="G28" s="83" t="s">
-        <v>433</v>
-      </c>
-      <c r="H28" s="81" t="s">
-        <v>248</v>
+      <c r="F28" s="103" t="s">
+        <v>281</v>
+      </c>
+      <c r="G28" s="128" t="s">
+        <v>388</v>
+      </c>
+      <c r="H28" s="80" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="79" t="s">
-        <v>318</v>
-      </c>
-      <c r="B29" s="101">
-        <v>4606246</v>
-      </c>
-      <c r="C29" s="101" t="s">
-        <v>386</v>
-      </c>
-      <c r="D29" s="101" t="s">
-        <v>387</v>
-      </c>
-      <c r="E29" s="80" t="s">
-        <v>280</v>
-      </c>
-      <c r="F29" s="103" t="s">
+        <v>331</v>
+      </c>
+      <c r="B29" s="107">
+        <v>4608684</v>
+      </c>
+      <c r="C29" s="107" t="s">
+        <v>362</v>
+      </c>
+      <c r="D29" s="108" t="s">
+        <v>320</v>
+      </c>
+      <c r="E29" s="81" t="s">
+        <v>324</v>
+      </c>
+      <c r="F29" s="81" t="s">
         <v>281</v>
       </c>
-      <c r="G29" s="128" t="s">
-        <v>388</v>
-      </c>
-      <c r="H29" s="80" t="s">
-        <v>61</v>
+      <c r="G29" s="83" t="s">
+        <v>363</v>
+      </c>
+      <c r="H29" s="81" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="79" t="s">
         <v>331</v>
       </c>
-      <c r="B30" s="107">
-        <v>4608684</v>
-      </c>
-      <c r="C30" s="107" t="s">
-        <v>362</v>
-      </c>
-      <c r="D30" s="108" t="s">
+      <c r="B30" s="101">
+        <v>4608685</v>
+      </c>
+      <c r="C30" s="101" t="s">
+        <v>339</v>
+      </c>
+      <c r="D30" s="102" t="s">
         <v>320</v>
       </c>
-      <c r="E30" s="81" t="s">
-        <v>324</v>
-      </c>
-      <c r="F30" s="81" t="s">
+      <c r="E30" s="80" t="s">
+        <v>321</v>
+      </c>
+      <c r="F30" s="80" t="s">
         <v>281</v>
       </c>
-      <c r="G30" s="83" t="s">
-        <v>363</v>
-      </c>
-      <c r="H30" s="81" t="s">
-        <v>53</v>
+      <c r="G30" s="128" t="s">
+        <v>340</v>
+      </c>
+      <c r="H30" s="80" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="79" t="s">
-        <v>331</v>
+        <v>318</v>
       </c>
       <c r="B31" s="101">
-        <v>4608685</v>
+        <v>4608544</v>
       </c>
       <c r="C31" s="101" t="s">
-        <v>339</v>
+        <v>355</v>
       </c>
       <c r="D31" s="102" t="s">
         <v>320</v>
       </c>
       <c r="E31" s="80" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="F31" s="80" t="s">
         <v>281</v>
       </c>
       <c r="G31" s="128" t="s">
-        <v>340</v>
+        <v>356</v>
       </c>
       <c r="H31" s="80" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="79" t="s">
+        <v>331</v>
+      </c>
+      <c r="B32" s="107">
+        <v>229316</v>
+      </c>
+      <c r="C32" s="107" t="s">
+        <v>394</v>
+      </c>
+      <c r="D32" s="108" t="s">
+        <v>387</v>
+      </c>
+      <c r="E32" s="109" t="s">
+        <v>280</v>
+      </c>
+      <c r="F32" s="81" t="s">
+        <v>333</v>
+      </c>
+      <c r="G32" s="127" t="s">
+        <v>395</v>
+      </c>
+      <c r="H32" s="81" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" s="112" t="s">
         <v>318</v>
       </c>
-      <c r="B32" s="101">
-        <v>4608544</v>
-      </c>
-      <c r="C32" s="101" t="s">
-        <v>355</v>
-      </c>
-      <c r="D32" s="102" t="s">
+      <c r="B33" s="101">
+        <v>4612050</v>
+      </c>
+      <c r="C33" s="101" t="s">
+        <v>323</v>
+      </c>
+      <c r="D33" s="102" t="s">
         <v>320</v>
       </c>
-      <c r="E32" s="80" t="s">
+      <c r="E33" s="103" t="s">
         <v>324</v>
       </c>
-      <c r="F32" s="80" t="s">
+      <c r="F33" s="80" t="s">
         <v>281</v>
       </c>
-      <c r="G32" s="128" t="s">
-        <v>356</v>
-      </c>
-      <c r="H32" s="80" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A33" s="79" t="s">
+      <c r="G33" s="82" t="s">
+        <v>325</v>
+      </c>
+      <c r="H33" s="80" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" s="79" t="s">
         <v>331</v>
       </c>
-      <c r="B33" s="107">
-        <v>229316</v>
-      </c>
-      <c r="C33" s="107" t="s">
-        <v>394</v>
-      </c>
-      <c r="D33" s="108" t="s">
-        <v>387</v>
-      </c>
-      <c r="E33" s="109" t="s">
-        <v>280</v>
-      </c>
-      <c r="F33" s="81" t="s">
-        <v>333</v>
-      </c>
-      <c r="G33" s="127" t="s">
-        <v>395</v>
-      </c>
-      <c r="H33" s="81" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A34" s="112" t="s">
-        <v>318</v>
-      </c>
       <c r="B34" s="101">
-        <v>4612050</v>
+        <v>4612228</v>
       </c>
       <c r="C34" s="101" t="s">
-        <v>323</v>
-      </c>
-      <c r="D34" s="102" t="s">
+        <v>422</v>
+      </c>
+      <c r="D34" s="101" t="s">
         <v>320</v>
       </c>
-      <c r="E34" s="103" t="s">
+      <c r="E34" s="80" t="s">
         <v>324</v>
       </c>
       <c r="F34" s="80" t="s">
         <v>281</v>
       </c>
       <c r="G34" s="82" t="s">
-        <v>325</v>
+        <v>423</v>
       </c>
       <c r="H34" s="80" t="s">
-        <v>106</v>
+        <v>139</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="79" t="s">
-        <v>331</v>
-      </c>
-      <c r="B35" s="101">
-        <v>4612228</v>
-      </c>
-      <c r="C35" s="101" t="s">
-        <v>422</v>
-      </c>
-      <c r="D35" s="101" t="s">
+        <v>341</v>
+      </c>
+      <c r="B35" s="107">
+        <v>9762281</v>
+      </c>
+      <c r="C35" s="107" t="s">
+        <v>342</v>
+      </c>
+      <c r="D35" s="108" t="s">
         <v>320</v>
       </c>
-      <c r="E35" s="80" t="s">
-        <v>324</v>
-      </c>
-      <c r="F35" s="80" t="s">
-        <v>281</v>
-      </c>
-      <c r="G35" s="82" t="s">
-        <v>423</v>
-      </c>
-      <c r="H35" s="80" t="s">
-        <v>139</v>
+      <c r="E35" s="109" t="s">
+        <v>321</v>
+      </c>
+      <c r="F35" s="81" t="s">
+        <v>333</v>
+      </c>
+      <c r="G35" s="127" t="s">
+        <v>343</v>
+      </c>
+      <c r="H35" s="81" t="s">
+        <v>344</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
@@ -37981,25 +37981,25 @@
         <v>341</v>
       </c>
       <c r="B36" s="107">
-        <v>9762281</v>
+        <v>214272</v>
       </c>
       <c r="C36" s="107" t="s">
-        <v>342</v>
+        <v>398</v>
       </c>
       <c r="D36" s="108" t="s">
-        <v>320</v>
+        <v>387</v>
       </c>
       <c r="E36" s="109" t="s">
-        <v>321</v>
+        <v>280</v>
       </c>
       <c r="F36" s="81" t="s">
         <v>333</v>
       </c>
       <c r="G36" s="127" t="s">
-        <v>343</v>
+        <v>399</v>
       </c>
       <c r="H36" s="81" t="s">
-        <v>344</v>
+        <v>400</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
@@ -38007,415 +38007,415 @@
         <v>341</v>
       </c>
       <c r="B37" s="107">
-        <v>214272</v>
+        <v>2440812</v>
       </c>
       <c r="C37" s="107" t="s">
-        <v>398</v>
+        <v>348</v>
       </c>
       <c r="D37" s="108" t="s">
-        <v>387</v>
+        <v>349</v>
       </c>
       <c r="E37" s="109" t="s">
-        <v>280</v>
+        <v>321</v>
       </c>
       <c r="F37" s="81" t="s">
         <v>333</v>
       </c>
       <c r="G37" s="127" t="s">
-        <v>399</v>
+        <v>350</v>
       </c>
       <c r="H37" s="81" t="s">
-        <v>400</v>
+        <v>162</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="79" t="s">
-        <v>341</v>
-      </c>
-      <c r="B38" s="107">
-        <v>2440812</v>
-      </c>
-      <c r="C38" s="107" t="s">
-        <v>348</v>
-      </c>
-      <c r="D38" s="108" t="s">
-        <v>349</v>
-      </c>
-      <c r="E38" s="109" t="s">
-        <v>321</v>
-      </c>
-      <c r="F38" s="81" t="s">
-        <v>333</v>
-      </c>
-      <c r="G38" s="127" t="s">
-        <v>350</v>
-      </c>
-      <c r="H38" s="81" t="s">
-        <v>162</v>
+        <v>318</v>
+      </c>
+      <c r="B38" s="101">
+        <v>4608559</v>
+      </c>
+      <c r="C38" s="101" t="s">
+        <v>373</v>
+      </c>
+      <c r="D38" s="102" t="s">
+        <v>320</v>
+      </c>
+      <c r="E38" s="103" t="s">
+        <v>327</v>
+      </c>
+      <c r="F38" s="80" t="s">
+        <v>281</v>
+      </c>
+      <c r="G38" s="82" t="s">
+        <v>374</v>
+      </c>
+      <c r="H38" s="80" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="79" t="s">
-        <v>318</v>
+        <v>331</v>
       </c>
       <c r="B39" s="101">
-        <v>4608559</v>
+        <v>4612243</v>
       </c>
       <c r="C39" s="101" t="s">
-        <v>373</v>
+        <v>414</v>
       </c>
       <c r="D39" s="102" t="s">
         <v>320</v>
       </c>
       <c r="E39" s="103" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="F39" s="80" t="s">
         <v>281</v>
       </c>
       <c r="G39" s="82" t="s">
-        <v>374</v>
+        <v>415</v>
       </c>
       <c r="H39" s="80" t="s">
-        <v>19</v>
+        <v>102</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="79" t="s">
         <v>331</v>
       </c>
-      <c r="B40" s="101">
-        <v>4612243</v>
-      </c>
-      <c r="C40" s="101" t="s">
-        <v>414</v>
-      </c>
-      <c r="D40" s="102" t="s">
-        <v>320</v>
-      </c>
-      <c r="E40" s="103" t="s">
-        <v>321</v>
-      </c>
-      <c r="F40" s="80" t="s">
+      <c r="B40" s="107">
+        <v>4606308</v>
+      </c>
+      <c r="C40" s="107" t="s">
+        <v>389</v>
+      </c>
+      <c r="D40" s="108" t="s">
+        <v>387</v>
+      </c>
+      <c r="E40" s="109" t="s">
+        <v>280</v>
+      </c>
+      <c r="F40" s="81" t="s">
         <v>281</v>
       </c>
-      <c r="G40" s="82" t="s">
-        <v>415</v>
-      </c>
-      <c r="H40" s="80" t="s">
-        <v>102</v>
+      <c r="G40" s="127" t="s">
+        <v>390</v>
+      </c>
+      <c r="H40" s="81" t="s">
+        <v>391</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="79" t="s">
         <v>331</v>
       </c>
-      <c r="B41" s="107">
-        <v>4606308</v>
-      </c>
-      <c r="C41" s="107" t="s">
-        <v>389</v>
-      </c>
-      <c r="D41" s="108" t="s">
-        <v>387</v>
-      </c>
-      <c r="E41" s="109" t="s">
-        <v>280</v>
-      </c>
-      <c r="F41" s="81" t="s">
-        <v>281</v>
-      </c>
-      <c r="G41" s="127" t="s">
-        <v>390</v>
-      </c>
-      <c r="H41" s="81" t="s">
-        <v>391</v>
+      <c r="B41" s="101">
+        <v>9634222</v>
+      </c>
+      <c r="C41" s="101" t="s">
+        <v>392</v>
+      </c>
+      <c r="D41" s="102" t="s">
+        <v>320</v>
+      </c>
+      <c r="E41" s="103" t="s">
+        <v>327</v>
+      </c>
+      <c r="F41" s="103" t="s">
+        <v>333</v>
+      </c>
+      <c r="G41" s="128" t="s">
+        <v>393</v>
+      </c>
+      <c r="H41" s="80" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="79" t="s">
-        <v>331</v>
-      </c>
-      <c r="B42" s="101">
-        <v>9634222</v>
-      </c>
-      <c r="C42" s="101" t="s">
-        <v>392</v>
-      </c>
-      <c r="D42" s="102" t="s">
+        <v>341</v>
+      </c>
+      <c r="B42" s="107">
+        <v>4608780</v>
+      </c>
+      <c r="C42" s="107" t="s">
+        <v>380</v>
+      </c>
+      <c r="D42" s="108" t="s">
         <v>320</v>
       </c>
-      <c r="E42" s="103" t="s">
+      <c r="E42" s="109" t="s">
         <v>327</v>
       </c>
-      <c r="F42" s="103" t="s">
-        <v>333</v>
-      </c>
-      <c r="G42" s="128" t="s">
-        <v>393</v>
-      </c>
-      <c r="H42" s="80" t="s">
-        <v>39</v>
+      <c r="F42" s="109" t="s">
+        <v>281</v>
+      </c>
+      <c r="G42" s="83" t="s">
+        <v>381</v>
+      </c>
+      <c r="H42" s="81" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="79" t="s">
         <v>341</v>
       </c>
-      <c r="B43" s="107">
-        <v>4608780</v>
-      </c>
-      <c r="C43" s="107" t="s">
-        <v>380</v>
-      </c>
-      <c r="D43" s="108" t="s">
+      <c r="B43" s="101">
+        <v>2475130</v>
+      </c>
+      <c r="C43" s="101" t="s">
+        <v>382</v>
+      </c>
+      <c r="D43" s="102" t="s">
         <v>320</v>
       </c>
-      <c r="E43" s="109" t="s">
+      <c r="E43" s="103" t="s">
         <v>327</v>
       </c>
-      <c r="F43" s="109" t="s">
-        <v>281</v>
-      </c>
-      <c r="G43" s="83" t="s">
-        <v>381</v>
-      </c>
-      <c r="H43" s="81" t="s">
-        <v>45</v>
+      <c r="F43" s="103" t="s">
+        <v>333</v>
+      </c>
+      <c r="G43" s="128" t="s">
+        <v>383</v>
+      </c>
+      <c r="H43" s="80" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="79" t="s">
-        <v>341</v>
+        <v>331</v>
       </c>
       <c r="B44" s="101">
-        <v>2475130</v>
+        <v>4608721</v>
       </c>
       <c r="C44" s="101" t="s">
-        <v>382</v>
+        <v>335</v>
       </c>
       <c r="D44" s="102" t="s">
         <v>320</v>
       </c>
       <c r="E44" s="103" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="F44" s="103" t="s">
-        <v>333</v>
-      </c>
-      <c r="G44" s="128" t="s">
-        <v>383</v>
+        <v>281</v>
+      </c>
+      <c r="G44" s="82" t="s">
+        <v>336</v>
       </c>
       <c r="H44" s="80" t="s">
-        <v>84</v>
+        <v>32</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="79" t="s">
         <v>331</v>
       </c>
-      <c r="B45" s="101">
-        <v>4608721</v>
-      </c>
-      <c r="C45" s="101" t="s">
-        <v>335</v>
-      </c>
-      <c r="D45" s="102" t="s">
+      <c r="B45" s="107">
+        <v>4612247</v>
+      </c>
+      <c r="C45" s="107" t="s">
+        <v>424</v>
+      </c>
+      <c r="D45" s="108" t="s">
         <v>320</v>
       </c>
-      <c r="E45" s="103" t="s">
-        <v>321</v>
-      </c>
-      <c r="F45" s="103" t="s">
+      <c r="E45" s="109" t="s">
+        <v>327</v>
+      </c>
+      <c r="F45" s="109" t="s">
         <v>281</v>
       </c>
-      <c r="G45" s="82" t="s">
-        <v>336</v>
-      </c>
-      <c r="H45" s="80" t="s">
-        <v>32</v>
+      <c r="G45" s="83" t="s">
+        <v>425</v>
+      </c>
+      <c r="H45" s="81" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="79" t="s">
-        <v>331</v>
-      </c>
-      <c r="B46" s="107">
-        <v>4612247</v>
-      </c>
-      <c r="C46" s="107" t="s">
-        <v>424</v>
-      </c>
-      <c r="D46" s="108" t="s">
+        <v>318</v>
+      </c>
+      <c r="B46" s="101">
+        <v>2448533</v>
+      </c>
+      <c r="C46" s="101" t="s">
+        <v>426</v>
+      </c>
+      <c r="D46" s="102" t="s">
         <v>320</v>
       </c>
-      <c r="E46" s="109" t="s">
-        <v>327</v>
-      </c>
-      <c r="F46" s="109" t="s">
-        <v>281</v>
-      </c>
-      <c r="G46" s="83" t="s">
-        <v>425</v>
-      </c>
-      <c r="H46" s="81" t="s">
-        <v>136</v>
+      <c r="E46" s="103" t="s">
+        <v>280</v>
+      </c>
+      <c r="F46" s="103" t="s">
+        <v>333</v>
+      </c>
+      <c r="G46" s="131" t="s">
+        <v>427</v>
+      </c>
+      <c r="H46" s="80" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="79" t="s">
-        <v>318</v>
-      </c>
-      <c r="B47" s="101">
-        <v>2448533</v>
-      </c>
-      <c r="C47" s="101" t="s">
-        <v>426</v>
-      </c>
-      <c r="D47" s="102" t="s">
+        <v>331</v>
+      </c>
+      <c r="B47" s="107">
+        <v>4612389</v>
+      </c>
+      <c r="C47" s="107" t="s">
+        <v>416</v>
+      </c>
+      <c r="D47" s="108" t="s">
         <v>320</v>
       </c>
-      <c r="E47" s="103" t="s">
-        <v>280</v>
-      </c>
-      <c r="F47" s="103" t="s">
-        <v>333</v>
-      </c>
-      <c r="G47" s="131" t="s">
-        <v>427</v>
-      </c>
-      <c r="H47" s="80" t="s">
-        <v>223</v>
+      <c r="E47" s="117" t="s">
+        <v>321</v>
+      </c>
+      <c r="F47" s="81" t="s">
+        <v>281</v>
+      </c>
+      <c r="G47" s="83" t="s">
+        <v>417</v>
+      </c>
+      <c r="H47" s="81" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="79" t="s">
-        <v>331</v>
-      </c>
-      <c r="B48" s="107">
-        <v>4612389</v>
-      </c>
-      <c r="C48" s="107" t="s">
-        <v>416</v>
-      </c>
-      <c r="D48" s="108" t="s">
+        <v>341</v>
+      </c>
+      <c r="B48" s="101">
+        <v>1381625</v>
+      </c>
+      <c r="C48" s="101" t="s">
+        <v>351</v>
+      </c>
+      <c r="D48" s="102" t="s">
         <v>320</v>
       </c>
-      <c r="E48" s="117" t="s">
+      <c r="E48" s="114" t="s">
         <v>321</v>
       </c>
-      <c r="F48" s="81" t="s">
-        <v>281</v>
-      </c>
-      <c r="G48" s="83" t="s">
-        <v>417</v>
-      </c>
-      <c r="H48" s="81" t="s">
-        <v>108</v>
+      <c r="F48" s="80" t="s">
+        <v>333</v>
+      </c>
+      <c r="G48" s="128" t="s">
+        <v>352</v>
+      </c>
+      <c r="H48" s="80" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" s="79" t="s">
         <v>341</v>
       </c>
-      <c r="B49" s="101">
-        <v>1381625</v>
-      </c>
-      <c r="C49" s="101" t="s">
-        <v>351</v>
-      </c>
-      <c r="D49" s="102" t="s">
+      <c r="B49" s="107">
+        <v>2430855</v>
+      </c>
+      <c r="C49" s="107" t="s">
+        <v>403</v>
+      </c>
+      <c r="D49" s="108" t="s">
         <v>320</v>
       </c>
-      <c r="E49" s="114" t="s">
-        <v>321</v>
-      </c>
-      <c r="F49" s="80" t="s">
+      <c r="E49" s="117" t="s">
+        <v>280</v>
+      </c>
+      <c r="F49" s="81" t="s">
         <v>333</v>
       </c>
-      <c r="G49" s="128" t="s">
-        <v>352</v>
-      </c>
-      <c r="H49" s="80" t="s">
-        <v>41</v>
+      <c r="G49" s="83" t="s">
+        <v>404</v>
+      </c>
+      <c r="H49" s="81" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="79" t="s">
         <v>341</v>
       </c>
-      <c r="B50" s="107">
-        <v>2430855</v>
-      </c>
-      <c r="C50" s="107" t="s">
-        <v>403</v>
-      </c>
-      <c r="D50" s="108" t="s">
+      <c r="B50" s="101">
+        <v>4612126</v>
+      </c>
+      <c r="C50" s="101" t="s">
+        <v>410</v>
+      </c>
+      <c r="D50" s="102" t="s">
         <v>320</v>
       </c>
-      <c r="E50" s="117" t="s">
-        <v>280</v>
-      </c>
-      <c r="F50" s="81" t="s">
-        <v>333</v>
-      </c>
-      <c r="G50" s="83" t="s">
-        <v>404</v>
-      </c>
-      <c r="H50" s="81" t="s">
-        <v>27</v>
+      <c r="E50" s="114" t="s">
+        <v>324</v>
+      </c>
+      <c r="F50" s="80" t="s">
+        <v>281</v>
+      </c>
+      <c r="G50" s="82" t="s">
+        <v>411</v>
+      </c>
+      <c r="H50" s="80" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" s="79" t="s">
-        <v>341</v>
-      </c>
-      <c r="B51" s="101">
-        <v>4612126</v>
-      </c>
-      <c r="C51" s="101" t="s">
-        <v>410</v>
-      </c>
-      <c r="D51" s="102" t="s">
+        <v>318</v>
+      </c>
+      <c r="B51" s="107">
+        <v>4612171</v>
+      </c>
+      <c r="C51" s="107" t="s">
+        <v>319</v>
+      </c>
+      <c r="D51" s="108" t="s">
         <v>320</v>
       </c>
-      <c r="E51" s="114" t="s">
-        <v>324</v>
-      </c>
-      <c r="F51" s="80" t="s">
+      <c r="E51" s="117" t="s">
+        <v>321</v>
+      </c>
+      <c r="F51" s="81" t="s">
         <v>281</v>
       </c>
-      <c r="G51" s="82" t="s">
-        <v>411</v>
-      </c>
-      <c r="H51" s="80" t="s">
-        <v>105</v>
+      <c r="G51" s="83" t="s">
+        <v>322</v>
+      </c>
+      <c r="H51" s="81" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" s="79" t="s">
-        <v>318</v>
-      </c>
-      <c r="B52" s="107">
-        <v>4612171</v>
-      </c>
-      <c r="C52" s="107" t="s">
-        <v>319</v>
-      </c>
-      <c r="D52" s="108" t="s">
+        <v>331</v>
+      </c>
+      <c r="B52" s="101">
+        <v>4612192</v>
+      </c>
+      <c r="C52" s="101" t="s">
+        <v>418</v>
+      </c>
+      <c r="D52" s="102" t="s">
         <v>320</v>
       </c>
-      <c r="E52" s="117" t="s">
-        <v>321</v>
-      </c>
-      <c r="F52" s="81" t="s">
+      <c r="E52" s="114" t="s">
+        <v>324</v>
+      </c>
+      <c r="F52" s="80" t="s">
         <v>281</v>
       </c>
-      <c r="G52" s="83" t="s">
-        <v>322</v>
-      </c>
-      <c r="H52" s="81" t="s">
-        <v>114</v>
+      <c r="G52" s="82" t="s">
+        <v>419</v>
+      </c>
+      <c r="H52" s="80" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
@@ -38423,339 +38423,312 @@
         <v>331</v>
       </c>
       <c r="B53" s="101">
-        <v>4612192</v>
+        <v>9634180</v>
       </c>
       <c r="C53" s="101" t="s">
-        <v>418</v>
+        <v>377</v>
       </c>
       <c r="D53" s="102" t="s">
         <v>320</v>
       </c>
       <c r="E53" s="114" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="F53" s="80" t="s">
-        <v>281</v>
+        <v>333</v>
       </c>
       <c r="G53" s="82" t="s">
-        <v>419</v>
+        <v>378</v>
       </c>
       <c r="H53" s="80" t="s">
-        <v>103</v>
+        <v>379</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" s="79" t="s">
-        <v>331</v>
-      </c>
-      <c r="B54" s="101">
-        <v>9634180</v>
-      </c>
-      <c r="C54" s="101" t="s">
-        <v>377</v>
-      </c>
-      <c r="D54" s="102" t="s">
-        <v>320</v>
-      </c>
-      <c r="E54" s="114" t="s">
-        <v>327</v>
+        <v>341</v>
+      </c>
+      <c r="B54" s="148">
+        <v>4604625</v>
+      </c>
+      <c r="C54" s="148" t="s">
+        <v>405</v>
+      </c>
+      <c r="D54" s="101" t="s">
+        <v>406</v>
+      </c>
+      <c r="E54" s="80" t="s">
+        <v>280</v>
       </c>
       <c r="F54" s="80" t="s">
+        <v>281</v>
+      </c>
+      <c r="G54" s="159" t="s">
+        <v>407</v>
+      </c>
+      <c r="H54" s="161" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" s="146" t="s">
+        <v>341</v>
+      </c>
+      <c r="B55" s="147">
+        <v>2460800</v>
+      </c>
+      <c r="C55" s="147" t="s">
+        <v>370</v>
+      </c>
+      <c r="D55" s="107" t="s">
+        <v>349</v>
+      </c>
+      <c r="E55" s="81" t="s">
+        <v>324</v>
+      </c>
+      <c r="F55" s="81" t="s">
         <v>333</v>
       </c>
-      <c r="G54" s="82" t="s">
-        <v>378</v>
-      </c>
-      <c r="H54" s="80" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A55" s="79" t="s">
-        <v>341</v>
-      </c>
-      <c r="B55" s="148">
-        <v>4604625</v>
-      </c>
-      <c r="C55" s="148" t="s">
-        <v>405</v>
-      </c>
-      <c r="D55" s="101" t="s">
-        <v>406</v>
-      </c>
-      <c r="E55" s="80" t="s">
-        <v>280</v>
-      </c>
-      <c r="F55" s="80" t="s">
-        <v>281</v>
-      </c>
-      <c r="G55" s="159" t="s">
-        <v>407</v>
-      </c>
-      <c r="H55" s="161" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A56" s="146" t="s">
-        <v>341</v>
-      </c>
-      <c r="B56" s="147">
-        <v>2460800</v>
-      </c>
-      <c r="C56" s="147" t="s">
-        <v>370</v>
-      </c>
-      <c r="D56" s="107" t="s">
-        <v>349</v>
-      </c>
-      <c r="E56" s="81" t="s">
-        <v>324</v>
-      </c>
-      <c r="F56" s="81" t="s">
-        <v>333</v>
-      </c>
-      <c r="G56" s="155" t="s">
+      <c r="G55" s="155" t="s">
         <v>371</v>
       </c>
-      <c r="H56" s="160" t="s">
+      <c r="H55" s="160" t="s">
         <v>372</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A1:G41 D30:D54 A33:A54 B42:B47 F42:G47">
-    <cfRule type="containsText" dxfId="50" priority="57" operator="containsText" text="MEC">
+  <conditionalFormatting sqref="D29:D53 A32:A53 B41:B46 F41:G46 A1:G40">
+    <cfRule type="containsText" dxfId="68" priority="56" operator="containsText" text="INST">
+      <formula>NOT(ISERROR(SEARCH("INST",A1)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="67" priority="57" operator="containsText" text="MEC">
       <formula>NOT(ISERROR(SEARCH("MEC",A1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="49" priority="56" operator="containsText" text="INST">
-      <formula>NOT(ISERROR(SEARCH("INST",A1)))</formula>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A47:G53">
+    <cfRule type="containsText" dxfId="66" priority="10" operator="containsText" text="ELET">
+      <formula>NOT(ISERROR(SEARCH("ELET",A47)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="65" priority="11" operator="containsText" text="INST">
+      <formula>NOT(ISERROR(SEARCH("INST",A47)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="64" priority="12" operator="containsText" text="MEC">
+      <formula>NOT(ISERROR(SEARCH("MEC",A47)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A48:G54">
-    <cfRule type="containsText" dxfId="48" priority="10" operator="containsText" text="ELET">
-      <formula>NOT(ISERROR(SEARCH("ELET",A48)))</formula>
+  <conditionalFormatting sqref="C42:C45">
+    <cfRule type="containsText" dxfId="63" priority="37" operator="containsText" text="ELET">
+      <formula>NOT(ISERROR(SEARCH("ELET",C42)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="47" priority="11" operator="containsText" text="INST">
-      <formula>NOT(ISERROR(SEARCH("INST",A48)))</formula>
+    <cfRule type="containsText" dxfId="62" priority="38" operator="containsText" text="INST">
+      <formula>NOT(ISERROR(SEARCH("INST",C42)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="46" priority="12" operator="containsText" text="MEC">
-      <formula>NOT(ISERROR(SEARCH("MEC",A48)))</formula>
+    <cfRule type="containsText" dxfId="61" priority="39" operator="containsText" text="MEC">
+      <formula>NOT(ISERROR(SEARCH("MEC",C42)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C43:C46">
-    <cfRule type="containsText" dxfId="45" priority="37" operator="containsText" text="ELET">
-      <formula>NOT(ISERROR(SEARCH("ELET",C43)))</formula>
+  <conditionalFormatting sqref="C41:E41 D42:E44 E44:E45 D45 C46:E46">
+    <cfRule type="containsText" dxfId="60" priority="71" operator="containsText" text="INST">
+      <formula>NOT(ISERROR(SEARCH("INST",C41)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="44" priority="38" operator="containsText" text="INST">
-      <formula>NOT(ISERROR(SEARCH("INST",C43)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="43" priority="39" operator="containsText" text="MEC">
-      <formula>NOT(ISERROR(SEARCH("MEC",C43)))</formula>
+    <cfRule type="containsText" dxfId="59" priority="72" operator="containsText" text="MEC">
+      <formula>NOT(ISERROR(SEARCH("MEC",C41)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C42:E42 D43:E45 E45:E46 D46 C47:E47">
-    <cfRule type="containsText" dxfId="42" priority="72" operator="containsText" text="MEC">
-      <formula>NOT(ISERROR(SEARCH("MEC",C42)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="41" priority="71" operator="containsText" text="INST">
-      <formula>NOT(ISERROR(SEARCH("INST",C42)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D30:D54 A33:A54 A1:G41 B42:B47 F42:G47">
-    <cfRule type="containsText" dxfId="40" priority="55" operator="containsText" text="ELET">
+  <conditionalFormatting sqref="D29:D53 A32:A53 B41:B46 F41:G46 A1:G40">
+    <cfRule type="containsText" dxfId="58" priority="55" operator="containsText" text="ELET">
       <formula>NOT(ISERROR(SEARCH("ELET",A1)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D43:E45 E45:E46 C42:E42 D46 C47:E47">
-    <cfRule type="containsText" dxfId="39" priority="70" operator="containsText" text="ELET">
-      <formula>NOT(ISERROR(SEARCH("ELET",C42)))</formula>
+  <conditionalFormatting sqref="D42:E44 E44:E45 C41:E41 D45 C46:E46">
+    <cfRule type="containsText" dxfId="57" priority="70" operator="containsText" text="ELET">
+      <formula>NOT(ISERROR(SEARCH("ELET",C41)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E14:E18">
-    <cfRule type="containsText" dxfId="38" priority="111" operator="containsText" text="MEC">
+    <cfRule type="containsText" dxfId="56" priority="109" operator="containsText" text="ELET">
+      <formula>NOT(ISERROR(SEARCH("ELET",E14)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="55" priority="110" operator="containsText" text="INST">
+      <formula>NOT(ISERROR(SEARCH("INST",E14)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="54" priority="111" operator="containsText" text="MEC">
       <formula>NOT(ISERROR(SEARCH("MEC",E14)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="37" priority="109" operator="containsText" text="ELET">
-      <formula>NOT(ISERROR(SEARCH("ELET",E14)))</formula>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E38">
+    <cfRule type="containsText" dxfId="53" priority="88" operator="containsText" text="ELET">
+      <formula>NOT(ISERROR(SEARCH("ELET",E38)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="36" priority="110" operator="containsText" text="INST">
-      <formula>NOT(ISERROR(SEARCH("INST",E14)))</formula>
+    <cfRule type="containsText" dxfId="52" priority="89" operator="containsText" text="INST">
+      <formula>NOT(ISERROR(SEARCH("INST",E38)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="51" priority="90" operator="containsText" text="MEC">
+      <formula>NOT(ISERROR(SEARCH("MEC",E38)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E39">
-    <cfRule type="containsText" dxfId="35" priority="89" operator="containsText" text="INST">
-      <formula>NOT(ISERROR(SEARCH("INST",E39)))</formula>
+  <conditionalFormatting sqref="E40">
+    <cfRule type="containsText" dxfId="50" priority="85" operator="containsText" text="ELET">
+      <formula>NOT(ISERROR(SEARCH("ELET",E40)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="34" priority="88" operator="containsText" text="ELET">
-      <formula>NOT(ISERROR(SEARCH("ELET",E39)))</formula>
+    <cfRule type="containsText" dxfId="49" priority="86" operator="containsText" text="INST">
+      <formula>NOT(ISERROR(SEARCH("INST",E40)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="33" priority="90" operator="containsText" text="MEC">
-      <formula>NOT(ISERROR(SEARCH("MEC",E39)))</formula>
+    <cfRule type="containsText" dxfId="48" priority="87" operator="containsText" text="MEC">
+      <formula>NOT(ISERROR(SEARCH("MEC",E40)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="47" priority="94" operator="containsText" text="ELET">
+      <formula>NOT(ISERROR(SEARCH("ELET",E40)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="46" priority="95" operator="containsText" text="INST">
+      <formula>NOT(ISERROR(SEARCH("INST",E40)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="45" priority="96" operator="containsText" text="MEC">
+      <formula>NOT(ISERROR(SEARCH("MEC",E40)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E41">
-    <cfRule type="containsText" dxfId="32" priority="95" operator="containsText" text="INST">
-      <formula>NOT(ISERROR(SEARCH("INST",E41)))</formula>
+  <conditionalFormatting sqref="E42">
+    <cfRule type="containsText" dxfId="44" priority="28" operator="containsText" text="ELET">
+      <formula>NOT(ISERROR(SEARCH("ELET",E42)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="31" priority="94" operator="containsText" text="ELET">
-      <formula>NOT(ISERROR(SEARCH("ELET",E41)))</formula>
+    <cfRule type="containsText" dxfId="43" priority="29" operator="containsText" text="INST">
+      <formula>NOT(ISERROR(SEARCH("INST",E42)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="30" priority="87" operator="containsText" text="MEC">
-      <formula>NOT(ISERROR(SEARCH("MEC",E41)))</formula>
+    <cfRule type="containsText" dxfId="42" priority="30" operator="containsText" text="MEC">
+      <formula>NOT(ISERROR(SEARCH("MEC",E42)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="29" priority="86" operator="containsText" text="INST">
-      <formula>NOT(ISERROR(SEARCH("INST",E41)))</formula>
+    <cfRule type="containsText" dxfId="41" priority="31" operator="containsText" text="ELET">
+      <formula>NOT(ISERROR(SEARCH("ELET",E42)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="28" priority="85" operator="containsText" text="ELET">
-      <formula>NOT(ISERROR(SEARCH("ELET",E41)))</formula>
+    <cfRule type="containsText" dxfId="40" priority="32" operator="containsText" text="INST">
+      <formula>NOT(ISERROR(SEARCH("INST",E42)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="27" priority="96" operator="containsText" text="MEC">
-      <formula>NOT(ISERROR(SEARCH("MEC",E41)))</formula>
+    <cfRule type="containsText" dxfId="39" priority="33" operator="containsText" text="MEC">
+      <formula>NOT(ISERROR(SEARCH("MEC",E42)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="38" priority="64" operator="containsText" text="ELET">
+      <formula>NOT(ISERROR(SEARCH("ELET",E42)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="37" priority="65" operator="containsText" text="INST">
+      <formula>NOT(ISERROR(SEARCH("INST",E42)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="36" priority="66" operator="containsText" text="MEC">
+      <formula>NOT(ISERROR(SEARCH("MEC",E42)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E43">
-    <cfRule type="containsText" dxfId="26" priority="33" operator="containsText" text="MEC">
-      <formula>NOT(ISERROR(SEARCH("MEC",E43)))</formula>
+  <conditionalFormatting sqref="E44">
+    <cfRule type="containsText" dxfId="35" priority="13" operator="containsText" text="ELET">
+      <formula>NOT(ISERROR(SEARCH("ELET",E44)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="25" priority="32" operator="containsText" text="INST">
-      <formula>NOT(ISERROR(SEARCH("INST",E43)))</formula>
+    <cfRule type="containsText" dxfId="34" priority="14" operator="containsText" text="INST">
+      <formula>NOT(ISERROR(SEARCH("INST",E44)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="24" priority="64" operator="containsText" text="ELET">
-      <formula>NOT(ISERROR(SEARCH("ELET",E43)))</formula>
+    <cfRule type="containsText" dxfId="33" priority="15" operator="containsText" text="MEC">
+      <formula>NOT(ISERROR(SEARCH("MEC",E44)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="23" priority="65" operator="containsText" text="INST">
-      <formula>NOT(ISERROR(SEARCH("INST",E43)))</formula>
+    <cfRule type="containsText" dxfId="32" priority="16" operator="containsText" text="ELET">
+      <formula>NOT(ISERROR(SEARCH("ELET",E44)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="22" priority="66" operator="containsText" text="MEC">
-      <formula>NOT(ISERROR(SEARCH("MEC",E43)))</formula>
+    <cfRule type="containsText" dxfId="31" priority="17" operator="containsText" text="INST">
+      <formula>NOT(ISERROR(SEARCH("INST",E44)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="21" priority="28" operator="containsText" text="ELET">
-      <formula>NOT(ISERROR(SEARCH("ELET",E43)))</formula>
+    <cfRule type="containsText" dxfId="30" priority="18" operator="containsText" text="MEC">
+      <formula>NOT(ISERROR(SEARCH("MEC",E44)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="20" priority="29" operator="containsText" text="INST">
-      <formula>NOT(ISERROR(SEARCH("INST",E43)))</formula>
+    <cfRule type="containsText" dxfId="29" priority="19" operator="containsText" text="ELET">
+      <formula>NOT(ISERROR(SEARCH("ELET",E44)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="19" priority="30" operator="containsText" text="MEC">
-      <formula>NOT(ISERROR(SEARCH("MEC",E43)))</formula>
+    <cfRule type="containsText" dxfId="28" priority="20" operator="containsText" text="INST">
+      <formula>NOT(ISERROR(SEARCH("INST",E44)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="18" priority="31" operator="containsText" text="ELET">
-      <formula>NOT(ISERROR(SEARCH("ELET",E43)))</formula>
+    <cfRule type="containsText" dxfId="27" priority="21" operator="containsText" text="MEC">
+      <formula>NOT(ISERROR(SEARCH("MEC",E44)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="26" priority="61" operator="containsText" text="ELET">
+      <formula>NOT(ISERROR(SEARCH("ELET",E44)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="25" priority="62" operator="containsText" text="INST">
+      <formula>NOT(ISERROR(SEARCH("INST",E44)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="24" priority="63" operator="containsText" text="MEC">
+      <formula>NOT(ISERROR(SEARCH("MEC",E44)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="23" priority="67" operator="containsText" text="ELET">
+      <formula>NOT(ISERROR(SEARCH("ELET",E44)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="22" priority="68" operator="containsText" text="INST">
+      <formula>NOT(ISERROR(SEARCH("INST",E44)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="21" priority="69" operator="containsText" text="MEC">
+      <formula>NOT(ISERROR(SEARCH("MEC",E44)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E45">
-    <cfRule type="containsText" dxfId="17" priority="67" operator="containsText" text="ELET">
-      <formula>NOT(ISERROR(SEARCH("ELET",E45)))</formula>
+  <conditionalFormatting sqref="E47:E53">
+    <cfRule type="containsText" dxfId="20" priority="1" operator="containsText" text="ELET">
+      <formula>NOT(ISERROR(SEARCH("ELET",E47)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="16" priority="68" operator="containsText" text="INST">
-      <formula>NOT(ISERROR(SEARCH("INST",E45)))</formula>
+    <cfRule type="containsText" dxfId="19" priority="2" operator="containsText" text="INST">
+      <formula>NOT(ISERROR(SEARCH("INST",E47)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="15" priority="69" operator="containsText" text="MEC">
-      <formula>NOT(ISERROR(SEARCH("MEC",E45)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="14" priority="20" operator="containsText" text="INST">
-      <formula>NOT(ISERROR(SEARCH("INST",E45)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="13" priority="18" operator="containsText" text="MEC">
-      <formula>NOT(ISERROR(SEARCH("MEC",E45)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="12" priority="17" operator="containsText" text="INST">
-      <formula>NOT(ISERROR(SEARCH("INST",E45)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="11" priority="16" operator="containsText" text="ELET">
-      <formula>NOT(ISERROR(SEARCH("ELET",E45)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="10" priority="15" operator="containsText" text="MEC">
-      <formula>NOT(ISERROR(SEARCH("MEC",E45)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="9" priority="14" operator="containsText" text="INST">
-      <formula>NOT(ISERROR(SEARCH("INST",E45)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="8" priority="19" operator="containsText" text="ELET">
-      <formula>NOT(ISERROR(SEARCH("ELET",E45)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="7" priority="13" operator="containsText" text="ELET">
-      <formula>NOT(ISERROR(SEARCH("ELET",E45)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="6" priority="63" operator="containsText" text="MEC">
-      <formula>NOT(ISERROR(SEARCH("MEC",E45)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="5" priority="21" operator="containsText" text="MEC">
-      <formula>NOT(ISERROR(SEARCH("MEC",E45)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="4" priority="61" operator="containsText" text="ELET">
-      <formula>NOT(ISERROR(SEARCH("ELET",E45)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="3" priority="62" operator="containsText" text="INST">
-      <formula>NOT(ISERROR(SEARCH("INST",E45)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E48:E54">
-    <cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="ELET">
-      <formula>NOT(ISERROR(SEARCH("ELET",E48)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="MEC">
-      <formula>NOT(ISERROR(SEARCH("MEC",E48)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="INST">
-      <formula>NOT(ISERROR(SEARCH("INST",E48)))</formula>
+    <cfRule type="containsText" dxfId="18" priority="3" operator="containsText" text="MEC">
+      <formula>NOT(ISERROR(SEARCH("MEC",E47)))</formula>
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
-    <hyperlink ref="G39" r:id="rId1" display="mailto:maria.santos8@petrobras.com.br" xr:uid="{6DCE59A4-69CC-4495-934B-1EAAB04CACB6}"/>
+    <hyperlink ref="G38" r:id="rId1" display="mailto:maria.santos8@petrobras.com.br" xr:uid="{6DCE59A4-69CC-4495-934B-1EAAB04CACB6}"/>
     <hyperlink ref="G20" r:id="rId2" display="mailto:felipecahet@petrobras.com.br" xr:uid="{77AF463E-0A64-43F4-BC8E-5647EB3D400D}"/>
-    <hyperlink ref="G42" r:id="rId3" display="mailto:rperez@petrobras.com.br" xr:uid="{6EE97548-2B71-4DF3-A4A6-569103DB9431}"/>
+    <hyperlink ref="G41" r:id="rId3" display="mailto:rperez@petrobras.com.br" xr:uid="{6EE97548-2B71-4DF3-A4A6-569103DB9431}"/>
     <hyperlink ref="G10" r:id="rId4" display="mailto:antonio.r.cunha@petrobras.com.br" xr:uid="{1E91DB09-C92F-4BE4-81B4-DBB62DF8F8C9}"/>
     <hyperlink ref="G19" r:id="rId5" display="mailto:fabio.unterman@petrobras.com.br" xr:uid="{4845E320-A459-4FED-A5A7-4C1DE89FB145}"/>
-    <hyperlink ref="G33" r:id="rId6" display="mailto:leandro.eloy@petrobras.com.br" xr:uid="{6879825C-8E62-4884-AE18-C5A59B3F4494}"/>
-    <hyperlink ref="G54" r:id="rId7" display="mailto:vledo@petrobras.com.br" xr:uid="{B470581A-8EFE-4735-8A8F-3AFCFE66B4AD}"/>
+    <hyperlink ref="G32" r:id="rId6" display="mailto:leandro.eloy@petrobras.com.br" xr:uid="{6879825C-8E62-4884-AE18-C5A59B3F4494}"/>
+    <hyperlink ref="G53" r:id="rId7" display="mailto:vledo@petrobras.com.br" xr:uid="{B470581A-8EFE-4735-8A8F-3AFCFE66B4AD}"/>
     <hyperlink ref="G12" r:id="rId8" display="mailto:aureojr@petrobras.com.br" xr:uid="{129A8AC4-9874-4883-A5C0-0A7B041505DB}"/>
-    <hyperlink ref="G41" r:id="rId9" display="mailto:pietro.konzgen@petrobras.com.br" xr:uid="{6A55BBBD-A11E-41BB-956D-B08558B70F91}"/>
-    <hyperlink ref="G45" r:id="rId10" display="mailto:reinaldo.merendaz@petrobras.com.br" xr:uid="{57D58735-F1CC-46C4-9291-9761A33E3D92}"/>
+    <hyperlink ref="G40" r:id="rId9" display="mailto:pietro.konzgen@petrobras.com.br" xr:uid="{6A55BBBD-A11E-41BB-956D-B08558B70F91}"/>
+    <hyperlink ref="G44" r:id="rId10" display="mailto:reinaldo.merendaz@petrobras.com.br" xr:uid="{57D58735-F1CC-46C4-9291-9761A33E3D92}"/>
     <hyperlink ref="G26" r:id="rId11" display="mailto:jorge.mariano@petrobras.com.br" xr:uid="{50455D42-71BD-4B19-83C9-1BD9E0681620}"/>
-    <hyperlink ref="G30" r:id="rId12" display="mailto:julio.fassarela@petrobras.com.br" xr:uid="{BC951C1E-5444-49FB-AB3A-81058FC4925A}"/>
-    <hyperlink ref="G29" r:id="rId13" display="mailto:julio.bento@petrobras.com.br" xr:uid="{A2070F71-E586-43E2-AB9A-86252385B75E}"/>
+    <hyperlink ref="G29" r:id="rId12" display="mailto:julio.fassarela@petrobras.com.br" xr:uid="{BC951C1E-5444-49FB-AB3A-81058FC4925A}"/>
+    <hyperlink ref="G28" r:id="rId13" display="mailto:julio.bento@petrobras.com.br" xr:uid="{A2070F71-E586-43E2-AB9A-86252385B75E}"/>
     <hyperlink ref="G16" r:id="rId14" display="mailto:eder.reis@petrobras.com.br" xr:uid="{FA4BE8A7-AAB0-451E-BAB2-3609062F2F31}"/>
-    <hyperlink ref="G32" r:id="rId15" display="mailto:kevin.cunha@petrobras.com.br" xr:uid="{B6CA32EA-0BD4-41AE-AC55-6278B8E3815D}"/>
+    <hyperlink ref="G31" r:id="rId15" display="mailto:kevin.cunha@petrobras.com.br" xr:uid="{B6CA32EA-0BD4-41AE-AC55-6278B8E3815D}"/>
     <hyperlink ref="G8" r:id="rId16" display="mailto:andre.sthel@petrobras.com.br" xr:uid="{6C24DE0B-2592-4252-8B23-D0C08BF08FDC}"/>
-    <hyperlink ref="G31" r:id="rId17" display="mailto:junio.matos@petrobras.com.br" xr:uid="{678A55ED-8AF6-4895-AF92-7758644067B3}"/>
+    <hyperlink ref="G30" r:id="rId17" display="mailto:junio.matos@petrobras.com.br" xr:uid="{678A55ED-8AF6-4895-AF92-7758644067B3}"/>
     <hyperlink ref="G22" r:id="rId18" display="mailto:flaviomarinho@petrobras.com.br" xr:uid="{6D441E26-891B-4BF0-AAE2-FC5E3BB62DA6}"/>
-    <hyperlink ref="G36" r:id="rId19" display="mailto:marsantos@petrobras.com.br" xr:uid="{41D917A4-91C6-43E9-B645-B1B720405339}"/>
-    <hyperlink ref="G43" r:id="rId20" display="mailto:rafaelventurini@petrobras.com.br" xr:uid="{91F6C435-35D6-423C-91E0-453A491506D4}"/>
-    <hyperlink ref="G37" r:id="rId21" display="mailto:marcelo.vaqueiro@petrobras.com.br" xr:uid="{D41A80F3-BEDB-4D89-AC9B-E34D2855849A}"/>
-    <hyperlink ref="G50" r:id="rId22" display="mailto:thiago_gomes@petrobras.com.br" xr:uid="{90E10407-A610-4206-B722-AD1869090713}"/>
+    <hyperlink ref="G35" r:id="rId19" display="mailto:marsantos@petrobras.com.br" xr:uid="{41D917A4-91C6-43E9-B645-B1B720405339}"/>
+    <hyperlink ref="G42" r:id="rId20" display="mailto:rafaelventurini@petrobras.com.br" xr:uid="{91F6C435-35D6-423C-91E0-453A491506D4}"/>
+    <hyperlink ref="G36" r:id="rId21" display="mailto:marcelo.vaqueiro@petrobras.com.br" xr:uid="{D41A80F3-BEDB-4D89-AC9B-E34D2855849A}"/>
+    <hyperlink ref="G49" r:id="rId22" display="mailto:thiago_gomes@petrobras.com.br" xr:uid="{90E10407-A610-4206-B722-AD1869090713}"/>
     <hyperlink ref="G18" r:id="rId23" display="mailto:er.amaral@petrobras.com.br" xr:uid="{8980DAFB-1D0B-40F4-9B8F-C79A7633AADE}"/>
-    <hyperlink ref="G44" r:id="rId24" display="mailto:raulalende@petrobras.com.br" xr:uid="{51054975-FA5C-4A0C-A01A-B69CB732A63B}"/>
+    <hyperlink ref="G43" r:id="rId24" display="mailto:raulalende@petrobras.com.br" xr:uid="{51054975-FA5C-4A0C-A01A-B69CB732A63B}"/>
     <hyperlink ref="G24" r:id="rId25" display="mailto:igorteixeira@petrobras.com.br" xr:uid="{0677F51D-D6E1-42FB-8D41-804F0200448C}"/>
     <hyperlink ref="G5" r:id="rId26" display="mailto:andi9@petrobras.com.br" xr:uid="{36983D8E-D5DF-48F7-A9B0-4015407C66DA}"/>
     <hyperlink ref="G15" r:id="rId27" display="mailto:diogosouza@petrobras.com.br" xr:uid="{6396E6FA-7DB7-4D95-BFE8-CF51675313BB}"/>
     <hyperlink ref="G6" r:id="rId28" display="mailto:al.larangeira@petrobras.com.br" xr:uid="{A25DF3BF-16C5-4C83-AF87-4A39D31D426A}"/>
-    <hyperlink ref="G49" r:id="rId29" display="mailto:tmenegussi@petrobras.com.br" xr:uid="{13E79D22-390C-4A62-B24D-E081E854F777}"/>
+    <hyperlink ref="G48" r:id="rId29" display="mailto:tmenegussi@petrobras.com.br" xr:uid="{13E79D22-390C-4A62-B24D-E081E854F777}"/>
     <hyperlink ref="G3" r:id="rId30" display="mailto:alexsandroviana@petrobras.com.br" xr:uid="{0F5F2A66-5A44-4C92-A0A4-B859996DF8E2}"/>
-    <hyperlink ref="G55" r:id="rId31" display="mailto:vinicius.s.duarte@petrobras.com.br" xr:uid="{F95A7D59-2BCD-4217-AE07-ADC6C4B3EEEB}"/>
-    <hyperlink ref="G52" r:id="rId32" display="mailto:tonicler.kutz@petrobras.com.br" xr:uid="{8148FB2B-31FF-4E9A-8543-0B445F7F5F0D}"/>
-    <hyperlink ref="G56" r:id="rId33" display="mailto:wellingtonmarques@petrobras.com.br" xr:uid="{462C1D85-8615-494C-9AD2-BC348EC6540B}"/>
-    <hyperlink ref="G38" r:id="rId34" display="mailto:marcioamaral@petrobras.com.br" xr:uid="{79A1BEEC-6561-4E80-ADA4-E16A09CA6377}"/>
+    <hyperlink ref="G54" r:id="rId31" display="mailto:vinicius.s.duarte@petrobras.com.br" xr:uid="{F95A7D59-2BCD-4217-AE07-ADC6C4B3EEEB}"/>
+    <hyperlink ref="G51" r:id="rId32" display="mailto:tonicler.kutz@petrobras.com.br" xr:uid="{8148FB2B-31FF-4E9A-8543-0B445F7F5F0D}"/>
+    <hyperlink ref="G55" r:id="rId33" display="mailto:wellingtonmarques@petrobras.com.br" xr:uid="{462C1D85-8615-494C-9AD2-BC348EC6540B}"/>
+    <hyperlink ref="G37" r:id="rId34" display="mailto:marcioamaral@petrobras.com.br" xr:uid="{79A1BEEC-6561-4E80-ADA4-E16A09CA6377}"/>
     <hyperlink ref="G13" r:id="rId35" display="mailto:breno.batista@petrobras.com.br" xr:uid="{E5718E05-0457-46FB-90CD-6978DE046201}"/>
     <hyperlink ref="G7" r:id="rId36" display="mailto:andre.silva35@petrobras.com.br" xr:uid="{E95F45A8-B622-4B83-AD58-ADBBF306AFDB}"/>
     <hyperlink ref="G14" r:id="rId37" display="mailto:dimitriaraujo@petrobras.com.br" xr:uid="{03E94FCA-A8E7-4FA2-B8F4-1DE96B4A532C}"/>
-    <hyperlink ref="G40" r:id="rId38" display="mailto:pablo.p.almeida@petrobras.com.br" xr:uid="{6FDCA26B-F418-47EE-9E53-A086561CD9B5}"/>
-    <hyperlink ref="G48" r:id="rId39" display="mailto:ronald.quaresma@petrobras.com.br" xr:uid="{509AB431-CB46-4BCD-8B40-4AA6AA0CA3C8}"/>
-    <hyperlink ref="G53" r:id="rId40" display="mailto:victor.f.campos@petrobras.com.br" xr:uid="{FF723D74-94A5-4DCF-A442-5478BEB2A421}"/>
+    <hyperlink ref="G39" r:id="rId38" display="mailto:pablo.p.almeida@petrobras.com.br" xr:uid="{6FDCA26B-F418-47EE-9E53-A086561CD9B5}"/>
+    <hyperlink ref="G47" r:id="rId39" display="mailto:ronald.quaresma@petrobras.com.br" xr:uid="{509AB431-CB46-4BCD-8B40-4AA6AA0CA3C8}"/>
+    <hyperlink ref="G52" r:id="rId40" display="mailto:victor.f.campos@petrobras.com.br" xr:uid="{FF723D74-94A5-4DCF-A442-5478BEB2A421}"/>
     <hyperlink ref="G25" r:id="rId41" display="mailto:jailton.conceicao@petrobras.com.br" xr:uid="{C353F43F-726D-4691-B055-C9DC84E296EF}"/>
-    <hyperlink ref="G35" r:id="rId42" display="mailto:luiz.serpa@petrobras.com.br" xr:uid="{3454AD81-EEF9-48A2-8C19-E7E0CEDF91EC}"/>
-    <hyperlink ref="G46" r:id="rId43" display="mailto:ricardo.uema@petrobras.com.br" xr:uid="{036CF863-7C3B-4157-A95F-CF65CE7B6A21}"/>
-    <hyperlink ref="G51" r:id="rId44" display="mailto:thielles.gustavo@petrobras.com.br" xr:uid="{4D52C687-5192-42FB-A5B3-B3FAE08E0F66}"/>
-    <hyperlink ref="G34" r:id="rId45" display="mailto:luiz.ramos3@petrobras.com.br" xr:uid="{2ED234A1-3650-40E9-A734-B45CD2740BA6}"/>
+    <hyperlink ref="G34" r:id="rId42" display="mailto:luiz.serpa@petrobras.com.br" xr:uid="{3454AD81-EEF9-48A2-8C19-E7E0CEDF91EC}"/>
+    <hyperlink ref="G45" r:id="rId43" display="mailto:ricardo.uema@petrobras.com.br" xr:uid="{036CF863-7C3B-4157-A95F-CF65CE7B6A21}"/>
+    <hyperlink ref="G50" r:id="rId44" display="mailto:thielles.gustavo@petrobras.com.br" xr:uid="{4D52C687-5192-42FB-A5B3-B3FAE08E0F66}"/>
+    <hyperlink ref="G33" r:id="rId45" display="mailto:luiz.ramos3@petrobras.com.br" xr:uid="{2ED234A1-3650-40E9-A734-B45CD2740BA6}"/>
     <hyperlink ref="G2" r:id="rId46" display="mailto:alexandre.martins@petrobras.com.br" xr:uid="{D35603D2-785F-4186-A05B-B9E5FFFCEE13}"/>
-    <hyperlink ref="G28" r:id="rId47" display="mailto:jluiscruz@petrobras.com.br" xr:uid="{13F92D62-CB2E-40D9-9BB3-F54C1EE81CB2}"/>
-    <hyperlink ref="G23" r:id="rId48" display="mailto:fredericoaugusto@petrobras.com.br" xr:uid="{942AE330-E7C9-4057-9CAC-9E85556BE03E}"/>
-    <hyperlink ref="G4" r:id="rId49" xr:uid="{C3D1EB3B-D93B-4AC6-9167-65F36C6A1D08}"/>
-    <hyperlink ref="G9" r:id="rId50" xr:uid="{4367D5A8-7A39-4BAA-B3B4-B6FAB3F558A4}"/>
-    <hyperlink ref="G11" r:id="rId51" xr:uid="{968FCC36-D4E6-49B2-9ADF-BBB5FC6DEE0C}"/>
-    <hyperlink ref="G27" r:id="rId52" xr:uid="{0F482F6C-3A68-4E8D-942C-1F1AF262D5E8}"/>
-    <hyperlink ref="G47" r:id="rId53" xr:uid="{DB981DA5-81E5-4D47-8E55-BFDDCC7C22D5}"/>
-    <hyperlink ref="G17" r:id="rId54" xr:uid="{F321162C-76E1-44DA-A125-159671836BDE}"/>
-    <hyperlink ref="G21" r:id="rId55" xr:uid="{F069D8EF-58D6-404D-AB9A-AD6AA1A37EA0}"/>
+    <hyperlink ref="G23" r:id="rId47" display="mailto:fredericoaugusto@petrobras.com.br" xr:uid="{942AE330-E7C9-4057-9CAC-9E85556BE03E}"/>
+    <hyperlink ref="G4" r:id="rId48" xr:uid="{C3D1EB3B-D93B-4AC6-9167-65F36C6A1D08}"/>
+    <hyperlink ref="G9" r:id="rId49" xr:uid="{4367D5A8-7A39-4BAA-B3B4-B6FAB3F558A4}"/>
+    <hyperlink ref="G11" r:id="rId50" xr:uid="{968FCC36-D4E6-49B2-9ADF-BBB5FC6DEE0C}"/>
+    <hyperlink ref="G27" r:id="rId51" xr:uid="{0F482F6C-3A68-4E8D-942C-1F1AF262D5E8}"/>
+    <hyperlink ref="G46" r:id="rId52" xr:uid="{DB981DA5-81E5-4D47-8E55-BFDDCC7C22D5}"/>
+    <hyperlink ref="G17" r:id="rId53" xr:uid="{F321162C-76E1-44DA-A125-159671836BDE}"/>
+    <hyperlink ref="G21" r:id="rId54" xr:uid="{F069D8EF-58D6-404D-AB9A-AD6AA1A37EA0}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -41402,57 +41375,57 @@
     <mergeCell ref="B2:E2"/>
   </mergeCells>
   <conditionalFormatting sqref="A96:A97">
-    <cfRule type="containsText" dxfId="68" priority="1" operator="containsText" text="ELET">
+    <cfRule type="containsText" dxfId="17" priority="1" operator="containsText" text="ELET">
       <formula>NOT(ISERROR(SEARCH("ELET",A96)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="67" priority="2" operator="containsText" text="INST">
+    <cfRule type="containsText" dxfId="16" priority="2" operator="containsText" text="INST">
       <formula>NOT(ISERROR(SEARCH("INST",A96)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="66" priority="3" operator="containsText" text="MEC">
+    <cfRule type="containsText" dxfId="15" priority="3" operator="containsText" text="MEC">
       <formula>NOT(ISERROR(SEARCH("MEC",A96)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A76:E97">
-    <cfRule type="containsText" dxfId="65" priority="16" operator="containsText" text="ELET">
+    <cfRule type="containsText" dxfId="14" priority="16" operator="containsText" text="ELET">
       <formula>NOT(ISERROR(SEARCH("ELET",A76)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="64" priority="17" operator="containsText" text="INST">
+    <cfRule type="containsText" dxfId="13" priority="17" operator="containsText" text="INST">
       <formula>NOT(ISERROR(SEARCH("INST",A76)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="63" priority="18" operator="containsText" text="MEC">
+    <cfRule type="containsText" dxfId="12" priority="18" operator="containsText" text="MEC">
       <formula>NOT(ISERROR(SEARCH("MEC",A76)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D92:D97">
-    <cfRule type="containsText" dxfId="62" priority="4" operator="containsText" text="ELET">
+    <cfRule type="containsText" dxfId="11" priority="4" operator="containsText" text="ELET">
       <formula>NOT(ISERROR(SEARCH("ELET",D92)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="61" priority="5" operator="containsText" text="INST">
+    <cfRule type="containsText" dxfId="10" priority="5" operator="containsText" text="INST">
       <formula>NOT(ISERROR(SEARCH("INST",D92)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="60" priority="6" operator="containsText" text="MEC">
+    <cfRule type="containsText" dxfId="9" priority="6" operator="containsText" text="MEC">
       <formula>NOT(ISERROR(SEARCH("MEC",D92)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E88:E89">
-    <cfRule type="containsText" dxfId="59" priority="13" operator="containsText" text="ELET">
+    <cfRule type="containsText" dxfId="8" priority="13" operator="containsText" text="ELET">
       <formula>NOT(ISERROR(SEARCH("ELET",E88)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="58" priority="14" operator="containsText" text="INST">
+    <cfRule type="containsText" dxfId="7" priority="14" operator="containsText" text="INST">
       <formula>NOT(ISERROR(SEARCH("INST",E88)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="57" priority="15" operator="containsText" text="MEC">
+    <cfRule type="containsText" dxfId="6" priority="15" operator="containsText" text="MEC">
       <formula>NOT(ISERROR(SEARCH("MEC",E88)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E89:E93">
-    <cfRule type="containsText" dxfId="56" priority="10" operator="containsText" text="ELET">
+    <cfRule type="containsText" dxfId="5" priority="10" operator="containsText" text="ELET">
       <formula>NOT(ISERROR(SEARCH("ELET",E89)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="55" priority="11" operator="containsText" text="INST">
+    <cfRule type="containsText" dxfId="4" priority="11" operator="containsText" text="INST">
       <formula>NOT(ISERROR(SEARCH("INST",E89)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="54" priority="12" operator="containsText" text="MEC">
+    <cfRule type="containsText" dxfId="3" priority="12" operator="containsText" text="MEC">
       <formula>NOT(ISERROR(SEARCH("MEC",E89)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -49878,11 +49851,24 @@
     </row>
   </sheetData>
   <mergeCells count="35">
-    <mergeCell ref="GW4:HC4"/>
-    <mergeCell ref="HD4:HJ4"/>
-    <mergeCell ref="HK4:HQ4"/>
-    <mergeCell ref="HR4:HX4"/>
-    <mergeCell ref="HY4:IE4"/>
+    <mergeCell ref="AD4:AJ4"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="I4:O4"/>
+    <mergeCell ref="P4:V4"/>
+    <mergeCell ref="W4:AC4"/>
+    <mergeCell ref="DJ4:DP4"/>
+    <mergeCell ref="AK4:AQ4"/>
+    <mergeCell ref="AR4:AX4"/>
+    <mergeCell ref="AY4:BE4"/>
+    <mergeCell ref="BF4:BL4"/>
+    <mergeCell ref="BM4:BS4"/>
+    <mergeCell ref="BT4:BZ4"/>
+    <mergeCell ref="CA4:CG4"/>
+    <mergeCell ref="CH4:CN4"/>
+    <mergeCell ref="CO4:CU4"/>
+    <mergeCell ref="CV4:DB4"/>
+    <mergeCell ref="DC4:DI4"/>
     <mergeCell ref="GP4:GV4"/>
     <mergeCell ref="DQ4:DW4"/>
     <mergeCell ref="DX4:ED4"/>
@@ -49895,24 +49881,11 @@
     <mergeCell ref="FU4:GA4"/>
     <mergeCell ref="GB4:GH4"/>
     <mergeCell ref="GI4:GO4"/>
-    <mergeCell ref="DJ4:DP4"/>
-    <mergeCell ref="AK4:AQ4"/>
-    <mergeCell ref="AR4:AX4"/>
-    <mergeCell ref="AY4:BE4"/>
-    <mergeCell ref="BF4:BL4"/>
-    <mergeCell ref="BM4:BS4"/>
-    <mergeCell ref="BT4:BZ4"/>
-    <mergeCell ref="CA4:CG4"/>
-    <mergeCell ref="CH4:CN4"/>
-    <mergeCell ref="CO4:CU4"/>
-    <mergeCell ref="CV4:DB4"/>
-    <mergeCell ref="DC4:DI4"/>
-    <mergeCell ref="AD4:AJ4"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="I4:O4"/>
-    <mergeCell ref="P4:V4"/>
-    <mergeCell ref="W4:AC4"/>
+    <mergeCell ref="GW4:HC4"/>
+    <mergeCell ref="HD4:HJ4"/>
+    <mergeCell ref="HK4:HQ4"/>
+    <mergeCell ref="HR4:HX4"/>
+    <mergeCell ref="HY4:IE4"/>
   </mergeCells>
   <conditionalFormatting sqref="D7:D31">
     <cfRule type="dataBar" priority="1">
@@ -49929,15 +49902,15 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I5:BL31 BM8:IE31 BM5:IE6">
-    <cfRule type="expression" dxfId="53" priority="4">
+    <cfRule type="expression" dxfId="2" priority="4">
       <formula>AND(TODAY()&gt;=I$5,TODAY()&lt;J$5)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I7:BL31 BM8:IE31">
-    <cfRule type="expression" dxfId="52" priority="2">
+    <cfRule type="expression" dxfId="1" priority="2">
       <formula>AND(Início_da_tarefa&lt;=I$5,ROUNDDOWN((Término_da_tarefa-Início_da_tarefa+1)*Progresso_da_tarefa,0)+Início_da_tarefa-1&gt;=I$5)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="51" priority="3" stopIfTrue="1">
+    <cfRule type="expression" dxfId="0" priority="3" stopIfTrue="1">
       <formula>AND(Término_da_tarefa&gt;=I$5,Início_da_tarefa&lt;J$5)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -50248,6 +50221,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="0d1dea18-7b56-4ac7-aa1d-7834839a8030" xsi:nil="true"/>
@@ -50257,15 +50239,6 @@
     <_Flow_SignoffStatus xmlns="a9f3451a-73cb-4405-a932-26db050e40a8" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -50288,6 +50261,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4A34E49-7289-4AEA-9593-4F55E04ADB10}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC3AD2E1-977A-4D4F-8EE8-D64B5FFADF75}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
@@ -50304,14 +50285,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4A34E49-7289-4AEA-9593-4F55E04ADB10}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{cdac03a7-e156-4c4b-b35d-d580a54520fa}" enabled="1" method="Privileged" siteId="{5b6f6241-9a57-4be4-8e50-1dfa72e79a57}" removed="0"/>
